--- a/south_africa/data/residential-property-price-indices-2010-to-2026.xlsx
+++ b/south_africa/data/residential-property-price-indices-2010-to-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DATA\econstats\Prices\P0160_RPPI\P0160\Releases_2026\202601\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DATA\econstats\Prices\P0160_RPPI\P0160\Releases_2026\202604\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24B7999-46DA-4892-9A05-1D18F1DAB5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3BA7B7-F496-4A71-81DF-CED610645586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F514C32-9796-49FD-B820-80002B255DE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="295">
   <si>
     <t>m201001</t>
   </si>
@@ -620,6 +617,15 @@
     <t>m202601</t>
   </si>
   <si>
+    <t>m202602</t>
+  </si>
+  <si>
+    <t>m202603</t>
+  </si>
+  <si>
+    <t>m202604</t>
+  </si>
+  <si>
     <t>Residential property price index: national and provincial indices</t>
   </si>
   <si>
@@ -921,13 +927,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -952,7 +964,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -981,39 +993,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1046,26 +1058,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1098,23 +1093,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1176,6 +1154,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1184,13 +1169,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1255,73 +1233,52 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699B8B45-BFA9-4EAC-B4A0-BE01459A346F}">
-  <dimension ref="A1:GT56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:GW56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="189" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="191" max="202" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="9" width="8.77734375" style="1"/>
+    <col min="10" max="205" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="1" t="s">
         <v>279</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="J1" t="s">
         <v>0</v>
@@ -1863,7 +1820,7 @@
       <c r="GG1" t="s">
         <v>179</v>
       </c>
-      <c r="GH1" s="1" t="s">
+      <c r="GH1" t="s">
         <v>180</v>
       </c>
       <c r="GI1" t="s">
@@ -1902,34 +1859,43 @@
       <c r="GT1" t="s">
         <v>192</v>
       </c>
+      <c r="GU1" t="s">
+        <v>193</v>
+      </c>
+      <c r="GV1" t="s">
+        <v>194</v>
+      </c>
+      <c r="GW1" t="s">
+        <v>195</v>
+      </c>
     </row>
-    <row r="2" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H2" t="s">
+      <c r="C2" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>285</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J2">
         <v>58.4</v>
@@ -2471,73 +2437,82 @@
       <c r="GG2">
         <v>116</v>
       </c>
-      <c r="GH2" s="1">
+      <c r="GH2">
         <v>116.2</v>
       </c>
       <c r="GI2">
-        <v>116.5</v>
+        <v>116.3</v>
       </c>
       <c r="GJ2">
-        <v>117.1</v>
+        <v>116.9</v>
       </c>
       <c r="GK2">
-        <v>117.8</v>
+        <v>117.6</v>
       </c>
       <c r="GL2">
-        <v>118.8</v>
+        <v>118.3</v>
       </c>
       <c r="GM2">
+        <v>118.9</v>
+      </c>
+      <c r="GN2">
         <v>119.5</v>
       </c>
-      <c r="GN2">
-        <v>120.2</v>
-      </c>
       <c r="GO2">
+        <v>120.1</v>
+      </c>
+      <c r="GP2">
         <v>120.8</v>
       </c>
-      <c r="GP2">
-        <v>121.5</v>
-      </c>
       <c r="GQ2">
-        <v>122.4</v>
+        <v>121.6</v>
       </c>
       <c r="GR2">
-        <v>123.3</v>
+        <v>122.6</v>
       </c>
       <c r="GS2">
+        <v>123.5</v>
+      </c>
+      <c r="GT2">
         <v>124.4</v>
       </c>
-      <c r="GT2">
+      <c r="GU2">
         <v>125.3</v>
       </c>
+      <c r="GV2">
+        <v>126.1</v>
+      </c>
+      <c r="GW2">
+        <v>126.9</v>
+      </c>
     </row>
-    <row r="3" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H3" t="s">
-        <v>284</v>
-      </c>
-      <c r="I3" t="s">
-        <v>285</v>
+      <c r="F3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J3">
         <v>49</v>
@@ -3079,73 +3054,82 @@
       <c r="GG3">
         <v>127</v>
       </c>
-      <c r="GH3" s="1">
+      <c r="GH3">
         <v>127.1</v>
       </c>
       <c r="GI3">
-        <v>127.4</v>
+        <v>127.2</v>
       </c>
       <c r="GJ3">
-        <v>128.30000000000001</v>
+        <v>128.5</v>
       </c>
       <c r="GK3">
-        <v>129.69999999999999</v>
+        <v>129.9</v>
       </c>
       <c r="GL3">
         <v>131.1</v>
       </c>
       <c r="GM3">
-        <v>132.5</v>
+        <v>132</v>
       </c>
       <c r="GN3">
-        <v>133.6</v>
+        <v>132.69999999999999</v>
       </c>
       <c r="GO3">
+        <v>133.4</v>
+      </c>
+      <c r="GP3">
         <v>134.4</v>
       </c>
-      <c r="GP3">
-        <v>135.19999999999999</v>
-      </c>
       <c r="GQ3">
-        <v>136.30000000000001</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="GR3">
-        <v>137.80000000000001</v>
+        <v>137.30000000000001</v>
       </c>
       <c r="GS3">
-        <v>139.4</v>
+        <v>139</v>
       </c>
       <c r="GT3">
-        <v>141.1</v>
+        <v>140.69999999999999</v>
+      </c>
+      <c r="GU3">
+        <v>142.1</v>
+      </c>
+      <c r="GV3">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="GW3">
+        <v>144.4</v>
       </c>
     </row>
-    <row r="4" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="B4" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H4" t="s">
+      <c r="C4" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I4" t="s">
-        <v>285</v>
+      <c r="D4" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J4">
         <v>61.3</v>
@@ -3687,73 +3671,82 @@
       <c r="GG4">
         <v>112.2</v>
       </c>
-      <c r="GH4" s="1">
+      <c r="GH4">
         <v>112</v>
       </c>
       <c r="GI4">
-        <v>111.9</v>
+        <v>112.1</v>
       </c>
       <c r="GJ4">
-        <v>111.9</v>
+        <v>112.2</v>
       </c>
       <c r="GK4">
-        <v>112.1</v>
+        <v>112.7</v>
       </c>
       <c r="GL4">
-        <v>112.4</v>
+        <v>113.4</v>
       </c>
       <c r="GM4">
-        <v>112.7</v>
+        <v>114.2</v>
       </c>
       <c r="GN4">
-        <v>113</v>
+        <v>114.8</v>
       </c>
       <c r="GO4">
-        <v>113.3</v>
+        <v>115.3</v>
       </c>
       <c r="GP4">
-        <v>113.8</v>
+        <v>115.7</v>
       </c>
       <c r="GQ4">
-        <v>114.2</v>
+        <v>116.1</v>
       </c>
       <c r="GR4">
-        <v>114.6</v>
+        <v>116.7</v>
       </c>
       <c r="GS4">
-        <v>115.1</v>
+        <v>117.4</v>
       </c>
       <c r="GT4">
-        <v>115.6</v>
+        <v>118.2</v>
+      </c>
+      <c r="GU4">
+        <v>118.8</v>
+      </c>
+      <c r="GV4">
+        <v>119.2</v>
+      </c>
+      <c r="GW4">
+        <v>119.5</v>
       </c>
     </row>
-    <row r="5" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="B5" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H5" t="s">
+      <c r="C5" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I5" t="s">
-        <v>285</v>
+      <c r="D5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J5">
         <v>44.8</v>
@@ -4295,73 +4288,82 @@
       <c r="GG5">
         <v>90.9</v>
       </c>
-      <c r="GH5" s="1">
+      <c r="GH5">
         <v>91.9</v>
       </c>
       <c r="GI5">
-        <v>93.1</v>
+        <v>92.5</v>
       </c>
       <c r="GJ5">
-        <v>94.5</v>
+        <v>93.9</v>
       </c>
       <c r="GK5">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="GL5">
-        <v>97.6</v>
+        <v>96.2</v>
       </c>
       <c r="GM5">
+        <v>97.4</v>
+      </c>
+      <c r="GN5">
+        <v>98.6</v>
+      </c>
+      <c r="GO5">
+        <v>99.2</v>
+      </c>
+      <c r="GP5">
         <v>99.1</v>
       </c>
-      <c r="GN5">
+      <c r="GQ5">
+        <v>98.3</v>
+      </c>
+      <c r="GR5">
+        <v>97.4</v>
+      </c>
+      <c r="GS5">
+        <v>97</v>
+      </c>
+      <c r="GT5">
+        <v>97.4</v>
+      </c>
+      <c r="GU5">
+        <v>98.7</v>
+      </c>
+      <c r="GV5">
         <v>100.2</v>
       </c>
-      <c r="GO5">
-        <v>101.1</v>
-      </c>
-      <c r="GP5">
+      <c r="GW5">
         <v>101.7</v>
       </c>
-      <c r="GQ5">
-        <v>102.1</v>
-      </c>
-      <c r="GR5">
-        <v>102.4</v>
-      </c>
-      <c r="GS5">
-        <v>102.3</v>
-      </c>
-      <c r="GT5">
-        <v>101.8</v>
-      </c>
     </row>
-    <row r="6" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="B6" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H6" t="s">
+      <c r="C6" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I6" t="s">
-        <v>285</v>
+      <c r="D6" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J6">
         <v>65.2</v>
@@ -4903,73 +4905,82 @@
       <c r="GG6">
         <v>119.1</v>
       </c>
-      <c r="GH6" s="1">
+      <c r="GH6">
         <v>119.9</v>
       </c>
       <c r="GI6">
-        <v>120.6</v>
+        <v>120.5</v>
       </c>
       <c r="GJ6">
-        <v>120.8</v>
+        <v>120.9</v>
       </c>
       <c r="GK6">
-        <v>120.9</v>
+        <v>121.4</v>
       </c>
       <c r="GL6">
-        <v>121.1</v>
+        <v>122</v>
       </c>
       <c r="GM6">
-        <v>121.5</v>
+        <v>122.4</v>
       </c>
       <c r="GN6">
+        <v>122.5</v>
+      </c>
+      <c r="GO6">
+        <v>122.3</v>
+      </c>
+      <c r="GP6">
         <v>122.1</v>
       </c>
-      <c r="GO6">
-        <v>122.9</v>
-      </c>
-      <c r="GP6">
-        <v>123.5</v>
-      </c>
       <c r="GQ6">
-        <v>123.9</v>
+        <v>122.2</v>
       </c>
       <c r="GR6">
-        <v>124.3</v>
+        <v>122.8</v>
       </c>
       <c r="GS6">
+        <v>123.7</v>
+      </c>
+      <c r="GT6">
         <v>124.8</v>
       </c>
-      <c r="GT6">
-        <v>125.5</v>
+      <c r="GU6">
+        <v>125.8</v>
+      </c>
+      <c r="GV6">
+        <v>126.6</v>
+      </c>
+      <c r="GW6">
+        <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="B7" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H7" t="s">
+      <c r="C7" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I7" t="s">
-        <v>285</v>
+      <c r="D7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J7">
         <v>61.8</v>
@@ -5511,73 +5522,82 @@
       <c r="GG7">
         <v>107</v>
       </c>
-      <c r="GH7" s="1">
+      <c r="GH7">
         <v>107.3</v>
       </c>
       <c r="GI7">
+        <v>106.9</v>
+      </c>
+      <c r="GJ7">
+        <v>107</v>
+      </c>
+      <c r="GK7">
+        <v>107</v>
+      </c>
+      <c r="GL7">
+        <v>106.9</v>
+      </c>
+      <c r="GM7">
+        <v>106.8</v>
+      </c>
+      <c r="GN7">
+        <v>106.9</v>
+      </c>
+      <c r="GO7">
+        <v>107.2</v>
+      </c>
+      <c r="GP7">
         <v>107.7</v>
       </c>
-      <c r="GJ7">
-        <v>108.3</v>
-      </c>
-      <c r="GK7">
-        <v>108.9</v>
-      </c>
-      <c r="GL7">
-        <v>109.4</v>
-      </c>
-      <c r="GM7">
-        <v>109.6</v>
-      </c>
-      <c r="GN7">
+      <c r="GQ7">
+        <v>108.4</v>
+      </c>
+      <c r="GR7">
+        <v>109</v>
+      </c>
+      <c r="GS7">
         <v>109.7</v>
       </c>
-      <c r="GO7">
-        <v>109.8</v>
-      </c>
-      <c r="GP7">
-        <v>110.3</v>
-      </c>
-      <c r="GQ7">
-        <v>111.2</v>
-      </c>
-      <c r="GR7">
-        <v>112.1</v>
-      </c>
-      <c r="GS7">
-        <v>112.9</v>
-      </c>
       <c r="GT7">
-        <v>113.2</v>
+        <v>110.1</v>
+      </c>
+      <c r="GU7">
+        <v>110.5</v>
+      </c>
+      <c r="GV7">
+        <v>110.9</v>
+      </c>
+      <c r="GW7">
+        <v>111.3</v>
       </c>
     </row>
-    <row r="8" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" t="s">
-        <v>206</v>
-      </c>
-      <c r="E8" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" t="s">
-        <v>205</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="B8" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H8" t="s">
+      <c r="C8" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I8" t="s">
-        <v>285</v>
+      <c r="D8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J8">
         <v>83.3</v>
@@ -6119,73 +6139,82 @@
       <c r="GG8">
         <v>127.6</v>
       </c>
-      <c r="GH8" s="1">
+      <c r="GH8">
         <v>128.6</v>
       </c>
       <c r="GI8">
-        <v>129.5</v>
+        <v>131.30000000000001</v>
       </c>
       <c r="GJ8">
+        <v>131.6</v>
+      </c>
+      <c r="GK8">
+        <v>131.1</v>
+      </c>
+      <c r="GL8">
+        <v>130.1</v>
+      </c>
+      <c r="GM8">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="GN8">
+        <v>127.7</v>
+      </c>
+      <c r="GO8">
+        <v>127.3</v>
+      </c>
+      <c r="GP8">
+        <v>127.8</v>
+      </c>
+      <c r="GQ8">
+        <v>128.9</v>
+      </c>
+      <c r="GR8">
         <v>130.4</v>
       </c>
-      <c r="GK8">
-        <v>131</v>
-      </c>
-      <c r="GL8">
-        <v>131.1</v>
-      </c>
-      <c r="GM8">
-        <v>131</v>
-      </c>
-      <c r="GN8">
-        <v>130.80000000000001</v>
-      </c>
-      <c r="GO8">
-        <v>130.80000000000001</v>
-      </c>
-      <c r="GP8">
-        <v>131.1</v>
-      </c>
-      <c r="GQ8">
-        <v>131.9</v>
-      </c>
-      <c r="GR8">
-        <v>133.30000000000001</v>
-      </c>
       <c r="GS8">
-        <v>135</v>
+        <v>132.1</v>
       </c>
       <c r="GT8">
-        <v>136.9</v>
+        <v>133.69999999999999</v>
+      </c>
+      <c r="GU8">
+        <v>135.4</v>
+      </c>
+      <c r="GV8">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="GW8">
+        <v>139.4</v>
       </c>
     </row>
-    <row r="9" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" t="s">
-        <v>281</v>
-      </c>
-      <c r="D9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F9" t="s">
-        <v>207</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="B9" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H9" t="s">
+      <c r="C9" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I9" t="s">
-        <v>285</v>
+      <c r="D9" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J9">
         <v>62.1</v>
@@ -6727,73 +6756,82 @@
       <c r="GG9">
         <v>107.9</v>
       </c>
-      <c r="GH9" s="1">
+      <c r="GH9">
         <v>107.9</v>
       </c>
       <c r="GI9">
-        <v>108</v>
+        <v>107.9</v>
       </c>
       <c r="GJ9">
-        <v>108.2</v>
+        <v>108.1</v>
       </c>
       <c r="GK9">
-        <v>108.5</v>
+        <v>108.4</v>
       </c>
       <c r="GL9">
         <v>108.8</v>
       </c>
       <c r="GM9">
-        <v>109.2</v>
+        <v>109.3</v>
       </c>
       <c r="GN9">
-        <v>109.7</v>
+        <v>109.8</v>
       </c>
       <c r="GO9">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="GP9">
-        <v>110.9</v>
+        <v>111</v>
       </c>
       <c r="GQ9">
         <v>111.4</v>
       </c>
       <c r="GR9">
-        <v>111.9</v>
+        <v>111.8</v>
       </c>
       <c r="GS9">
+        <v>112.1</v>
+      </c>
+      <c r="GT9">
         <v>112.4</v>
       </c>
-      <c r="GT9">
-        <v>112.8</v>
+      <c r="GU9">
+        <v>112.7</v>
+      </c>
+      <c r="GV9">
+        <v>113.1</v>
+      </c>
+      <c r="GW9">
+        <v>113.6</v>
       </c>
     </row>
-    <row r="10" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>280</v>
-      </c>
-      <c r="C10" t="s">
-        <v>281</v>
-      </c>
-      <c r="D10" t="s">
-        <v>210</v>
-      </c>
-      <c r="E10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F10" t="s">
-        <v>209</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="B10" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H10" t="s">
+      <c r="C10" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I10" t="s">
-        <v>285</v>
+      <c r="D10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J10">
         <v>74.2</v>
@@ -7335,73 +7373,82 @@
       <c r="GG10">
         <v>121.6</v>
       </c>
-      <c r="GH10" s="1">
+      <c r="GH10">
         <v>122.8</v>
       </c>
       <c r="GI10">
-        <v>124.6</v>
+        <v>124.7</v>
       </c>
       <c r="GJ10">
-        <v>126.3</v>
+        <v>125.7</v>
       </c>
       <c r="GK10">
+        <v>126.7</v>
+      </c>
+      <c r="GL10">
         <v>127.7</v>
       </c>
-      <c r="GL10">
-        <v>128.69999999999999</v>
-      </c>
       <c r="GM10">
-        <v>129.30000000000001</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="GN10">
+        <v>129</v>
+      </c>
+      <c r="GO10">
         <v>130.1</v>
       </c>
-      <c r="GO10">
-        <v>131.1</v>
-      </c>
       <c r="GP10">
-        <v>132.30000000000001</v>
+        <v>131.4</v>
       </c>
       <c r="GQ10">
-        <v>133.69999999999999</v>
+        <v>132.6</v>
       </c>
       <c r="GR10">
-        <v>135</v>
+        <v>133.6</v>
       </c>
       <c r="GS10">
-        <v>135.69999999999999</v>
+        <v>134.4</v>
       </c>
       <c r="GT10">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="GU10">
         <v>135.9</v>
       </c>
+      <c r="GV10">
+        <v>136.69999999999999</v>
+      </c>
+      <c r="GW10">
+        <v>137.4</v>
+      </c>
     </row>
-    <row r="11" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" t="s">
-        <v>193</v>
-      </c>
-      <c r="F11" t="s">
-        <v>211</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="B11" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H11" t="s">
+      <c r="C11" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I11" t="s">
-        <v>285</v>
+      <c r="D11" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="J11">
         <v>86.7</v>
@@ -7943,73 +7990,82 @@
       <c r="GG11">
         <v>119.7</v>
       </c>
-      <c r="GH11" s="1">
+      <c r="GH11">
         <v>120.9</v>
       </c>
       <c r="GI11">
-        <v>122.4</v>
+        <v>122.1</v>
       </c>
       <c r="GJ11">
-        <v>124.1</v>
+        <v>122.6</v>
       </c>
       <c r="GK11">
+        <v>123.6</v>
+      </c>
+      <c r="GL11">
         <v>125.9</v>
       </c>
-      <c r="GL11">
-        <v>128.30000000000001</v>
-      </c>
       <c r="GM11">
-        <v>131.5</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="GN11">
-        <v>134.80000000000001</v>
+        <v>133</v>
       </c>
       <c r="GO11">
-        <v>137.80000000000001</v>
+        <v>136.5</v>
       </c>
       <c r="GP11">
-        <v>140.19999999999999</v>
+        <v>138.4</v>
       </c>
       <c r="GQ11">
-        <v>142.1</v>
+        <v>139</v>
       </c>
       <c r="GR11">
-        <v>143.30000000000001</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="GS11">
-        <v>143.5</v>
+        <v>136.9</v>
       </c>
       <c r="GT11">
-        <v>143.30000000000001</v>
+        <v>135.6</v>
+      </c>
+      <c r="GU11">
+        <v>135</v>
+      </c>
+      <c r="GV11">
+        <v>135.1</v>
+      </c>
+      <c r="GW11">
+        <v>135.4</v>
       </c>
     </row>
-    <row r="12" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>280</v>
-      </c>
-      <c r="C12" t="s">
-        <v>281</v>
-      </c>
-      <c r="D12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="B12" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G12" t="s">
-        <v>283</v>
-      </c>
-      <c r="H12" t="s">
-        <v>284</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H12" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J12">
         <v>57.4</v>
@@ -8551,73 +8607,82 @@
       <c r="GG12">
         <v>112.8</v>
       </c>
-      <c r="GH12" s="1">
+      <c r="GH12">
         <v>112.9</v>
       </c>
       <c r="GI12">
-        <v>113.1</v>
+        <v>112.8</v>
       </c>
       <c r="GJ12">
-        <v>113.5</v>
+        <v>113.3</v>
       </c>
       <c r="GK12">
-        <v>114.2</v>
+        <v>113.9</v>
       </c>
       <c r="GL12">
-        <v>114.9</v>
+        <v>114.6</v>
       </c>
       <c r="GM12">
-        <v>115.7</v>
+        <v>115.3</v>
       </c>
       <c r="GN12">
-        <v>116.5</v>
+        <v>116</v>
       </c>
       <c r="GO12">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="GP12">
-        <v>118</v>
+        <v>117.4</v>
       </c>
       <c r="GQ12">
-        <v>118.8</v>
+        <v>118.2</v>
       </c>
       <c r="GR12">
+        <v>118.9</v>
+      </c>
+      <c r="GS12">
         <v>119.6</v>
       </c>
-      <c r="GS12">
-        <v>120.5</v>
-      </c>
       <c r="GT12">
-        <v>121.4</v>
+        <v>120.4</v>
+      </c>
+      <c r="GU12">
+        <v>121.1</v>
+      </c>
+      <c r="GV12">
+        <v>121.8</v>
+      </c>
+      <c r="GW12">
+        <v>122.5</v>
       </c>
     </row>
-    <row r="13" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" t="s">
-        <v>281</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B13" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E13" t="s">
-        <v>213</v>
-      </c>
-      <c r="F13" t="s">
-        <v>215</v>
-      </c>
-      <c r="G13" t="s">
-        <v>283</v>
-      </c>
-      <c r="H13" t="s">
-        <v>284</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="F13" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J13">
         <v>47.6</v>
@@ -9159,73 +9224,82 @@
       <c r="GG13">
         <v>120.5</v>
       </c>
-      <c r="GH13" s="1">
+      <c r="GH13">
         <v>120.6</v>
       </c>
       <c r="GI13">
-        <v>120.9</v>
+        <v>120.5</v>
       </c>
       <c r="GJ13">
-        <v>121.7</v>
+        <v>121.4</v>
       </c>
       <c r="GK13">
-        <v>122.9</v>
+        <v>122.6</v>
       </c>
       <c r="GL13">
-        <v>124.3</v>
+        <v>123.7</v>
       </c>
       <c r="GM13">
-        <v>125.7</v>
+        <v>124.8</v>
       </c>
       <c r="GN13">
-        <v>126.9</v>
+        <v>125.8</v>
       </c>
       <c r="GO13">
-        <v>127.9</v>
+        <v>126.7</v>
       </c>
       <c r="GP13">
+        <v>127.8</v>
+      </c>
+      <c r="GQ13">
         <v>128.9</v>
       </c>
-      <c r="GQ13">
-        <v>130</v>
-      </c>
       <c r="GR13">
-        <v>131.5</v>
+        <v>130.1</v>
       </c>
       <c r="GS13">
-        <v>132.9</v>
+        <v>131.4</v>
       </c>
       <c r="GT13">
-        <v>134.5</v>
+        <v>132.69999999999999</v>
+      </c>
+      <c r="GU13">
+        <v>133.9</v>
+      </c>
+      <c r="GV13">
+        <v>135</v>
+      </c>
+      <c r="GW13">
+        <v>136.1</v>
       </c>
     </row>
-    <row r="14" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" t="s">
-        <v>281</v>
-      </c>
-      <c r="D14" t="s">
-        <v>218</v>
-      </c>
-      <c r="E14" t="s">
-        <v>213</v>
-      </c>
-      <c r="F14" t="s">
-        <v>217</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="B14" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H14" t="s">
+      <c r="C14" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I14" t="s">
+      <c r="D14" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J14">
         <v>62.3</v>
@@ -9767,73 +9841,82 @@
       <c r="GG14">
         <v>102.5</v>
       </c>
-      <c r="GH14" s="1">
+      <c r="GH14">
         <v>101.5</v>
       </c>
       <c r="GI14">
-        <v>100.8</v>
+        <v>102.5</v>
       </c>
       <c r="GJ14">
-        <v>100.5</v>
+        <v>103.3</v>
       </c>
       <c r="GK14">
-        <v>100.6</v>
+        <v>104.3</v>
       </c>
       <c r="GL14">
-        <v>100.8</v>
+        <v>105.6</v>
       </c>
       <c r="GM14">
-        <v>101.3</v>
+        <v>106.9</v>
       </c>
       <c r="GN14">
-        <v>102</v>
+        <v>108.2</v>
       </c>
       <c r="GO14">
-        <v>103</v>
+        <v>109.4</v>
       </c>
       <c r="GP14">
-        <v>104.4</v>
+        <v>110.2</v>
       </c>
       <c r="GQ14">
-        <v>105.5</v>
+        <v>110.2</v>
       </c>
       <c r="GR14">
-        <v>106.5</v>
+        <v>109.6</v>
       </c>
       <c r="GS14">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="GT14">
-        <v>107.2</v>
+        <v>108.6</v>
+      </c>
+      <c r="GU14">
+        <v>108.4</v>
+      </c>
+      <c r="GV14">
+        <v>108.8</v>
+      </c>
+      <c r="GW14">
+        <v>109.5</v>
       </c>
     </row>
-    <row r="15" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>280</v>
-      </c>
-      <c r="C15" t="s">
-        <v>281</v>
-      </c>
-      <c r="D15" t="s">
-        <v>220</v>
-      </c>
-      <c r="E15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" t="s">
-        <v>219</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="B15" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H15" t="s">
+      <c r="C15" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I15" t="s">
+      <c r="D15" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J15">
         <v>61.1</v>
@@ -10375,73 +10458,82 @@
       <c r="GG15">
         <v>117.1</v>
       </c>
-      <c r="GH15" s="1">
+      <c r="GH15">
         <v>117.2</v>
       </c>
       <c r="GI15">
-        <v>117.3</v>
+        <v>116.9</v>
       </c>
       <c r="GJ15">
+        <v>116.7</v>
+      </c>
+      <c r="GK15">
+        <v>117</v>
+      </c>
+      <c r="GL15">
         <v>117.4</v>
       </c>
-      <c r="GK15">
-        <v>117.7</v>
-      </c>
-      <c r="GL15">
-        <v>118</v>
-      </c>
       <c r="GM15">
+        <v>117.8</v>
+      </c>
+      <c r="GN15">
         <v>118.2</v>
       </c>
-      <c r="GN15">
+      <c r="GO15">
         <v>118.4</v>
       </c>
-      <c r="GO15">
-        <v>118.5</v>
-      </c>
       <c r="GP15">
-        <v>118.5</v>
+        <v>118.7</v>
       </c>
       <c r="GQ15">
-        <v>118.5</v>
+        <v>119.3</v>
       </c>
       <c r="GR15">
-        <v>118.9</v>
+        <v>120.5</v>
       </c>
       <c r="GS15">
-        <v>119.4</v>
+        <v>121.7</v>
       </c>
       <c r="GT15">
-        <v>120</v>
+        <v>123</v>
+      </c>
+      <c r="GU15">
+        <v>123.8</v>
+      </c>
+      <c r="GV15">
+        <v>124.3</v>
+      </c>
+      <c r="GW15">
+        <v>124.5</v>
       </c>
     </row>
-    <row r="16" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="16" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>280</v>
-      </c>
-      <c r="C16" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" t="s">
-        <v>222</v>
-      </c>
-      <c r="E16" t="s">
-        <v>213</v>
-      </c>
-      <c r="F16" t="s">
-        <v>221</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="B16" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H16" t="s">
+      <c r="C16" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I16" t="s">
+      <c r="D16" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J16">
         <v>64.7</v>
@@ -10983,73 +11075,82 @@
       <c r="GG16">
         <v>121</v>
       </c>
-      <c r="GH16" s="1">
+      <c r="GH16">
         <v>122</v>
       </c>
       <c r="GI16">
-        <v>122.8</v>
+        <v>122.9</v>
       </c>
       <c r="GJ16">
-        <v>123.2</v>
+        <v>123.5</v>
       </c>
       <c r="GK16">
-        <v>123.5</v>
+        <v>123.8</v>
       </c>
       <c r="GL16">
-        <v>123.8</v>
+        <v>124.3</v>
       </c>
       <c r="GM16">
+        <v>124.4</v>
+      </c>
+      <c r="GN16">
+        <v>124.4</v>
+      </c>
+      <c r="GO16">
+        <v>124.2</v>
+      </c>
+      <c r="GP16">
+        <v>123.9</v>
+      </c>
+      <c r="GQ16">
         <v>124.1</v>
       </c>
-      <c r="GN16">
-        <v>124.5</v>
-      </c>
-      <c r="GO16">
-        <v>125</v>
-      </c>
-      <c r="GP16">
-        <v>125.5</v>
-      </c>
-      <c r="GQ16">
-        <v>126</v>
-      </c>
       <c r="GR16">
-        <v>126.2</v>
+        <v>124.4</v>
       </c>
       <c r="GS16">
-        <v>126.6</v>
+        <v>125.2</v>
       </c>
       <c r="GT16">
-        <v>127</v>
+        <v>125.9</v>
+      </c>
+      <c r="GU16">
+        <v>126.5</v>
+      </c>
+      <c r="GV16">
+        <v>126.9</v>
+      </c>
+      <c r="GW16">
+        <v>127.3</v>
       </c>
     </row>
-    <row r="17" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>280</v>
-      </c>
-      <c r="C17" t="s">
-        <v>281</v>
-      </c>
-      <c r="D17" t="s">
-        <v>224</v>
-      </c>
-      <c r="E17" t="s">
-        <v>213</v>
-      </c>
-      <c r="F17" t="s">
-        <v>223</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="B17" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H17" t="s">
+      <c r="C17" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I17" t="s">
+      <c r="D17" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J17">
         <v>63.3</v>
@@ -11591,73 +11692,82 @@
       <c r="GG17">
         <v>107.9</v>
       </c>
-      <c r="GH17" s="1">
+      <c r="GH17">
         <v>108.4</v>
       </c>
       <c r="GI17">
+        <v>108.2</v>
+      </c>
+      <c r="GJ17">
+        <v>108.3</v>
+      </c>
+      <c r="GK17">
+        <v>108.5</v>
+      </c>
+      <c r="GL17">
+        <v>108.6</v>
+      </c>
+      <c r="GM17">
         <v>108.8</v>
       </c>
-      <c r="GJ17">
-        <v>109.3</v>
-      </c>
-      <c r="GK17">
-        <v>109.7</v>
-      </c>
-      <c r="GL17">
-        <v>110.2</v>
-      </c>
-      <c r="GM17">
-        <v>110.6</v>
-      </c>
       <c r="GN17">
-        <v>110.8</v>
+        <v>109</v>
       </c>
       <c r="GO17">
-        <v>111.1</v>
+        <v>109.4</v>
       </c>
       <c r="GP17">
-        <v>111.6</v>
+        <v>109.9</v>
       </c>
       <c r="GQ17">
+        <v>110.4</v>
+      </c>
+      <c r="GR17">
+        <v>111</v>
+      </c>
+      <c r="GS17">
+        <v>111.4</v>
+      </c>
+      <c r="GT17">
+        <v>111.7</v>
+      </c>
+      <c r="GU17">
+        <v>112</v>
+      </c>
+      <c r="GV17">
         <v>112.2</v>
       </c>
-      <c r="GR17">
-        <v>112.8</v>
-      </c>
-      <c r="GS17">
-        <v>113.3</v>
-      </c>
-      <c r="GT17">
-        <v>113.7</v>
+      <c r="GW17">
+        <v>112.5</v>
       </c>
     </row>
-    <row r="18" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C18" t="s">
-        <v>281</v>
-      </c>
-      <c r="D18" t="s">
-        <v>226</v>
-      </c>
-      <c r="E18" t="s">
-        <v>213</v>
-      </c>
-      <c r="F18" t="s">
-        <v>225</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="B18" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H18" t="s">
+      <c r="C18" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I18" t="s">
+      <c r="D18" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J18">
         <v>63.4</v>
@@ -12199,73 +12309,82 @@
       <c r="GG18">
         <v>110.3</v>
       </c>
-      <c r="GH18" s="1">
+      <c r="GH18">
         <v>110.6</v>
       </c>
       <c r="GI18">
         <v>111</v>
       </c>
       <c r="GJ18">
-        <v>111.4</v>
+        <v>111.1</v>
       </c>
       <c r="GK18">
-        <v>111.7</v>
+        <v>111.1</v>
       </c>
       <c r="GL18">
-        <v>111.8</v>
+        <v>111.2</v>
       </c>
       <c r="GM18">
+        <v>111.5</v>
+      </c>
+      <c r="GN18">
         <v>111.9</v>
-      </c>
-      <c r="GN18">
-        <v>112.2</v>
       </c>
       <c r="GO18">
         <v>112.6</v>
       </c>
       <c r="GP18">
-        <v>113.2</v>
+        <v>113.3</v>
       </c>
       <c r="GQ18">
-        <v>113.9</v>
+        <v>114.2</v>
       </c>
       <c r="GR18">
-        <v>114.5</v>
+        <v>114.8</v>
       </c>
       <c r="GS18">
-        <v>115.1</v>
+        <v>115.2</v>
       </c>
       <c r="GT18">
         <v>115.5</v>
       </c>
+      <c r="GU18">
+        <v>115.7</v>
+      </c>
+      <c r="GV18">
+        <v>116.1</v>
+      </c>
+      <c r="GW18">
+        <v>116.5</v>
+      </c>
     </row>
-    <row r="19" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>280</v>
-      </c>
-      <c r="C19" t="s">
-        <v>281</v>
-      </c>
-      <c r="D19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E19" t="s">
-        <v>213</v>
-      </c>
-      <c r="F19" t="s">
-        <v>227</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="B19" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H19" t="s">
+      <c r="C19" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I19" t="s">
+      <c r="D19" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J19">
         <v>62.6</v>
@@ -12807,23 +12926,23 @@
       <c r="GG19">
         <v>102.8</v>
       </c>
-      <c r="GH19" s="1">
+      <c r="GH19">
         <v>102.9</v>
       </c>
       <c r="GI19">
-        <v>103.1</v>
+        <v>102.9</v>
       </c>
       <c r="GJ19">
+        <v>103</v>
+      </c>
+      <c r="GK19">
         <v>103.3</v>
       </c>
-      <c r="GK19">
-        <v>103.6</v>
-      </c>
       <c r="GL19">
-        <v>103.9</v>
+        <v>103.7</v>
       </c>
       <c r="GM19">
-        <v>104.4</v>
+        <v>104.2</v>
       </c>
       <c r="GN19">
         <v>104.9</v>
@@ -12835,45 +12954,54 @@
         <v>106</v>
       </c>
       <c r="GQ19">
-        <v>106.6</v>
+        <v>106.4</v>
       </c>
       <c r="GR19">
-        <v>107.1</v>
+        <v>106.7</v>
       </c>
       <c r="GS19">
+        <v>107</v>
+      </c>
+      <c r="GT19">
         <v>107.4</v>
       </c>
-      <c r="GT19">
-        <v>107.7</v>
+      <c r="GU19">
+        <v>107.8</v>
+      </c>
+      <c r="GV19">
+        <v>108.3</v>
+      </c>
+      <c r="GW19">
+        <v>108.9</v>
       </c>
     </row>
-    <row r="20" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C20" t="s">
-        <v>281</v>
-      </c>
-      <c r="D20" t="s">
-        <v>230</v>
-      </c>
-      <c r="E20" t="s">
-        <v>213</v>
-      </c>
-      <c r="F20" t="s">
-        <v>229</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="B20" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H20" t="s">
+      <c r="C20" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I20" t="s">
+      <c r="D20" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>287</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="J20">
         <v>60.4</v>
@@ -13415,73 +13543,82 @@
       <c r="GG20">
         <v>112</v>
       </c>
-      <c r="GH20" s="1">
+      <c r="GH20">
         <v>111.6</v>
       </c>
       <c r="GI20">
-        <v>111.3</v>
+        <v>111.4</v>
       </c>
       <c r="GJ20">
-        <v>111.2</v>
+        <v>111.8</v>
       </c>
       <c r="GK20">
-        <v>111.4</v>
+        <v>112.3</v>
       </c>
       <c r="GL20">
-        <v>111.9</v>
+        <v>112.9</v>
       </c>
       <c r="GM20">
-        <v>112.5</v>
+        <v>113.5</v>
       </c>
       <c r="GN20">
-        <v>113.2</v>
+        <v>114</v>
       </c>
       <c r="GO20">
-        <v>113.8</v>
+        <v>114.4</v>
       </c>
       <c r="GP20">
-        <v>114.4</v>
+        <v>114.8</v>
       </c>
       <c r="GQ20">
-        <v>114.9</v>
+        <v>115.1</v>
       </c>
       <c r="GR20">
         <v>115.3</v>
       </c>
       <c r="GS20">
+        <v>115.5</v>
+      </c>
+      <c r="GT20">
         <v>115.7</v>
       </c>
-      <c r="GT20">
-        <v>116.1</v>
+      <c r="GU20">
+        <v>116</v>
+      </c>
+      <c r="GV20">
+        <v>116.3</v>
+      </c>
+      <c r="GW20">
+        <v>116.6</v>
       </c>
     </row>
-    <row r="21" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="21" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>280</v>
-      </c>
-      <c r="C21" t="s">
-        <v>281</v>
-      </c>
-      <c r="D21" t="s">
-        <v>232</v>
-      </c>
-      <c r="E21" t="s">
-        <v>231</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="B21" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G21" t="s">
-        <v>283</v>
-      </c>
-      <c r="H21" t="s">
-        <v>284</v>
-      </c>
-      <c r="I21" t="s">
-        <v>288</v>
+      <c r="H21" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J21">
         <v>57.7</v>
@@ -14023,73 +14160,82 @@
       <c r="GG21">
         <v>117.2</v>
       </c>
-      <c r="GH21" s="1">
+      <c r="GH21">
         <v>117.5</v>
       </c>
       <c r="GI21">
-        <v>117.9</v>
+        <v>117.4</v>
       </c>
       <c r="GJ21">
-        <v>118.4</v>
+        <v>118</v>
       </c>
       <c r="GK21">
-        <v>119.1</v>
+        <v>118.7</v>
       </c>
       <c r="GL21">
-        <v>119.9</v>
+        <v>119.3</v>
       </c>
       <c r="GM21">
-        <v>120.5</v>
+        <v>119.7</v>
       </c>
       <c r="GN21">
-        <v>120.9</v>
+        <v>119.8</v>
       </c>
       <c r="GO21">
-        <v>120.9</v>
+        <v>119.8</v>
       </c>
       <c r="GP21">
-        <v>120.8</v>
+        <v>119.8</v>
       </c>
       <c r="GQ21">
-        <v>120.5</v>
+        <v>120</v>
       </c>
       <c r="GR21">
         <v>120.2</v>
       </c>
       <c r="GS21">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="GT21">
-        <v>119.8</v>
+        <v>120.7</v>
+      </c>
+      <c r="GU21">
+        <v>120.6</v>
+      </c>
+      <c r="GV21">
+        <v>120.4</v>
+      </c>
+      <c r="GW21">
+        <v>120.2</v>
       </c>
     </row>
-    <row r="22" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>280</v>
-      </c>
-      <c r="C22" t="s">
-        <v>281</v>
-      </c>
-      <c r="D22" t="s">
-        <v>233</v>
-      </c>
-      <c r="E22" t="s">
-        <v>231</v>
-      </c>
-      <c r="F22" t="s">
-        <v>215</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="B22" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H22" t="s">
+      <c r="C22" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I22" t="s">
-        <v>288</v>
+      <c r="D22" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J22">
         <v>45.1</v>
@@ -14631,73 +14777,82 @@
       <c r="GG22">
         <v>116.3</v>
       </c>
-      <c r="GH22" s="1">
+      <c r="GH22">
         <v>117</v>
       </c>
       <c r="GI22">
-        <v>117.6</v>
+        <v>116.4</v>
       </c>
       <c r="GJ22">
+        <v>117.2</v>
+      </c>
+      <c r="GK22">
+        <v>118.4</v>
+      </c>
+      <c r="GL22">
+        <v>119.5</v>
+      </c>
+      <c r="GM22">
+        <v>120.1</v>
+      </c>
+      <c r="GN22">
+        <v>120.1</v>
+      </c>
+      <c r="GO22">
+        <v>119.7</v>
+      </c>
+      <c r="GP22">
+        <v>119.3</v>
+      </c>
+      <c r="GQ22">
+        <v>119.1</v>
+      </c>
+      <c r="GR22">
+        <v>119.2</v>
+      </c>
+      <c r="GS22">
+        <v>119.3</v>
+      </c>
+      <c r="GT22">
+        <v>119.1</v>
+      </c>
+      <c r="GU22">
         <v>118.3</v>
       </c>
-      <c r="GK22">
-        <v>119.3</v>
-      </c>
-      <c r="GL22">
-        <v>120.4</v>
-      </c>
-      <c r="GM22">
-        <v>121.3</v>
-      </c>
-      <c r="GN22">
-        <v>121.7</v>
-      </c>
-      <c r="GO22">
-        <v>121.7</v>
-      </c>
-      <c r="GP22">
-        <v>121.2</v>
-      </c>
-      <c r="GQ22">
-        <v>120.4</v>
-      </c>
-      <c r="GR22">
-        <v>119.5</v>
-      </c>
-      <c r="GS22">
-        <v>118.8</v>
-      </c>
-      <c r="GT22">
-        <v>118.2</v>
+      <c r="GV22">
+        <v>117</v>
+      </c>
+      <c r="GW22">
+        <v>115.7</v>
       </c>
     </row>
-    <row r="23" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>280</v>
-      </c>
-      <c r="C23" t="s">
-        <v>281</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="B23" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E23" t="s">
-        <v>231</v>
-      </c>
-      <c r="F23" t="s">
-        <v>217</v>
-      </c>
-      <c r="G23" t="s">
-        <v>283</v>
-      </c>
-      <c r="H23" t="s">
-        <v>284</v>
-      </c>
-      <c r="I23" t="s">
-        <v>288</v>
+      <c r="F23" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J23">
         <v>77.900000000000006</v>
@@ -15239,73 +15394,82 @@
       <c r="GG23">
         <v>81.7</v>
       </c>
-      <c r="GH23" s="1">
+      <c r="GH23">
         <v>80.3</v>
       </c>
       <c r="GI23">
-        <v>79.7</v>
+        <v>78.3</v>
       </c>
       <c r="GJ23">
-        <v>80.099999999999994</v>
+        <v>79.3</v>
       </c>
       <c r="GK23">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="GL23">
-        <v>82.5</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="GM23">
-        <v>83.8</v>
+        <v>82.2</v>
       </c>
       <c r="GN23">
-        <v>84.6</v>
+        <v>81.5</v>
       </c>
       <c r="GO23">
-        <v>84.1</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="GP23">
-        <v>82.2</v>
+        <v>77.8</v>
       </c>
       <c r="GQ23">
-        <v>79.400000000000006</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="GR23">
-        <v>76.5</v>
+        <v>74</v>
       </c>
       <c r="GS23">
-        <v>74.400000000000006</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="GT23">
-        <v>73.5</v>
+        <v>73.599999999999994</v>
+      </c>
+      <c r="GU23">
+        <v>74</v>
+      </c>
+      <c r="GV23">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="GW23">
+        <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>280</v>
-      </c>
-      <c r="C24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D24" t="s">
-        <v>235</v>
-      </c>
-      <c r="E24" t="s">
-        <v>231</v>
-      </c>
-      <c r="F24" t="s">
-        <v>219</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="B24" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H24" t="s">
+      <c r="C24" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I24" t="s">
-        <v>288</v>
+      <c r="D24" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J24">
         <v>43.5</v>
@@ -15847,73 +16011,82 @@
       <c r="GG24">
         <v>134.19999999999999</v>
       </c>
-      <c r="GH24" s="1">
+      <c r="GH24">
         <v>132.4</v>
       </c>
       <c r="GI24">
-        <v>131.69999999999999</v>
+        <v>130.9</v>
       </c>
       <c r="GJ24">
-        <v>131.80000000000001</v>
+        <v>132</v>
       </c>
       <c r="GK24">
-        <v>132.5</v>
+        <v>133.19999999999999</v>
       </c>
       <c r="GL24">
-        <v>133.4</v>
+        <v>133.6</v>
       </c>
       <c r="GM24">
-        <v>133.69999999999999</v>
+        <v>133.1</v>
       </c>
       <c r="GN24">
-        <v>133</v>
+        <v>131.19999999999999</v>
       </c>
       <c r="GO24">
-        <v>131.69999999999999</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="GP24">
-        <v>130.30000000000001</v>
+        <v>127</v>
       </c>
       <c r="GQ24">
-        <v>129.9</v>
+        <v>126.3</v>
       </c>
       <c r="GR24">
-        <v>130.9</v>
+        <v>126.6</v>
       </c>
       <c r="GS24">
-        <v>132.80000000000001</v>
+        <v>127.8</v>
       </c>
       <c r="GT24">
-        <v>135.5</v>
+        <v>129.19999999999999</v>
+      </c>
+      <c r="GU24">
+        <v>130.4</v>
+      </c>
+      <c r="GV24">
+        <v>131.30000000000001</v>
+      </c>
+      <c r="GW24">
+        <v>132.19999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>280</v>
-      </c>
-      <c r="C25" t="s">
-        <v>281</v>
-      </c>
-      <c r="D25" t="s">
-        <v>236</v>
-      </c>
-      <c r="E25" t="s">
-        <v>231</v>
-      </c>
-      <c r="F25" t="s">
-        <v>221</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="B25" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H25" t="s">
+      <c r="C25" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I25" t="s">
-        <v>288</v>
+      <c r="D25" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J25">
         <v>52.5</v>
@@ -16455,73 +16628,82 @@
       <c r="GG25">
         <v>97.5</v>
       </c>
-      <c r="GH25" s="1">
+      <c r="GH25">
         <v>97.6</v>
       </c>
       <c r="GI25">
-        <v>98.8</v>
+        <v>96.9</v>
       </c>
       <c r="GJ25">
-        <v>100.7</v>
+        <v>99.6</v>
       </c>
       <c r="GK25">
-        <v>103.6</v>
+        <v>102.9</v>
       </c>
       <c r="GL25">
-        <v>106.9</v>
+        <v>106.3</v>
       </c>
       <c r="GM25">
-        <v>110.2</v>
+        <v>109.3</v>
       </c>
       <c r="GN25">
-        <v>112.7</v>
+        <v>111.9</v>
       </c>
       <c r="GO25">
-        <v>114.4</v>
+        <v>114.2</v>
       </c>
       <c r="GP25">
-        <v>115.5</v>
+        <v>116.4</v>
       </c>
       <c r="GQ25">
-        <v>116.8</v>
+        <v>118.7</v>
       </c>
       <c r="GR25">
-        <v>118.3</v>
+        <v>120.9</v>
       </c>
       <c r="GS25">
-        <v>120</v>
+        <v>123.1</v>
       </c>
       <c r="GT25">
-        <v>121.7</v>
+        <v>125.1</v>
+      </c>
+      <c r="GU25">
+        <v>126.8</v>
+      </c>
+      <c r="GV25">
+        <v>128.30000000000001</v>
+      </c>
+      <c r="GW25">
+        <v>129.30000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="26" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>280</v>
-      </c>
-      <c r="C26" t="s">
-        <v>281</v>
-      </c>
-      <c r="D26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E26" t="s">
-        <v>231</v>
-      </c>
-      <c r="F26" t="s">
-        <v>223</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="B26" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H26" t="s">
+      <c r="C26" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I26" t="s">
-        <v>288</v>
+      <c r="D26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J26">
         <v>70.400000000000006</v>
@@ -17063,73 +17245,82 @@
       <c r="GG26">
         <v>99.3</v>
       </c>
-      <c r="GH26" s="1">
+      <c r="GH26">
         <v>98.3</v>
       </c>
       <c r="GI26">
-        <v>97.2</v>
+        <v>98.4</v>
       </c>
       <c r="GJ26">
+        <v>99.5</v>
+      </c>
+      <c r="GK26">
+        <v>99.8</v>
+      </c>
+      <c r="GL26">
+        <v>100.4</v>
+      </c>
+      <c r="GM26">
+        <v>101.2</v>
+      </c>
+      <c r="GN26">
+        <v>101.8</v>
+      </c>
+      <c r="GO26">
+        <v>101.8</v>
+      </c>
+      <c r="GP26">
+        <v>101.3</v>
+      </c>
+      <c r="GQ26">
+        <v>99.9</v>
+      </c>
+      <c r="GR26">
+        <v>98.1</v>
+      </c>
+      <c r="GS26">
+        <v>96.7</v>
+      </c>
+      <c r="GT26">
+        <v>95.9</v>
+      </c>
+      <c r="GU26">
+        <v>95.9</v>
+      </c>
+      <c r="GV26">
         <v>96.4</v>
       </c>
-      <c r="GK26">
-        <v>96.2</v>
-      </c>
-      <c r="GL26">
-        <v>96.8</v>
-      </c>
-      <c r="GM26">
-        <v>98.1</v>
-      </c>
-      <c r="GN26">
-        <v>99.7</v>
-      </c>
-      <c r="GO26">
-        <v>101.1</v>
-      </c>
-      <c r="GP26">
-        <v>101.5</v>
-      </c>
-      <c r="GQ26">
-        <v>100.6</v>
-      </c>
-      <c r="GR26">
-        <v>99.1</v>
-      </c>
-      <c r="GS26">
-        <v>97.2</v>
-      </c>
-      <c r="GT26">
-        <v>95.7</v>
+      <c r="GW26">
+        <v>96.9</v>
       </c>
     </row>
-    <row r="27" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>280</v>
-      </c>
-      <c r="C27" t="s">
-        <v>281</v>
-      </c>
-      <c r="D27" t="s">
-        <v>238</v>
-      </c>
-      <c r="E27" t="s">
-        <v>231</v>
-      </c>
-      <c r="F27" t="s">
-        <v>225</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="B27" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H27" t="s">
+      <c r="C27" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I27" t="s">
-        <v>288</v>
+      <c r="D27" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J27">
         <v>61.1</v>
@@ -17671,73 +17862,82 @@
       <c r="GG27">
         <v>118.6</v>
       </c>
-      <c r="GH27" s="1">
+      <c r="GH27">
         <v>119.4</v>
       </c>
       <c r="GI27">
-        <v>120.2</v>
+        <v>120.4</v>
       </c>
       <c r="GJ27">
-        <v>120.7</v>
+        <v>120</v>
       </c>
       <c r="GK27">
-        <v>121</v>
+        <v>119.7</v>
       </c>
       <c r="GL27">
-        <v>121.1</v>
+        <v>119.2</v>
       </c>
       <c r="GM27">
-        <v>121.1</v>
+        <v>118.7</v>
       </c>
       <c r="GN27">
-        <v>121.1</v>
+        <v>118.4</v>
       </c>
       <c r="GO27">
-        <v>121</v>
+        <v>118.4</v>
       </c>
       <c r="GP27">
+        <v>118.6</v>
+      </c>
+      <c r="GQ27">
+        <v>119.2</v>
+      </c>
+      <c r="GR27">
+        <v>120</v>
+      </c>
+      <c r="GS27">
         <v>120.9</v>
       </c>
-      <c r="GQ27">
-        <v>120.9</v>
-      </c>
-      <c r="GR27">
-        <v>120.9</v>
-      </c>
-      <c r="GS27">
-        <v>121.1</v>
-      </c>
       <c r="GT27">
-        <v>121.2</v>
+        <v>121.6</v>
+      </c>
+      <c r="GU27">
+        <v>122.3</v>
+      </c>
+      <c r="GV27">
+        <v>122.9</v>
+      </c>
+      <c r="GW27">
+        <v>123.4</v>
       </c>
     </row>
-    <row r="28" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="28" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>280</v>
-      </c>
-      <c r="C28" t="s">
-        <v>281</v>
-      </c>
-      <c r="D28" t="s">
-        <v>239</v>
-      </c>
-      <c r="E28" t="s">
-        <v>231</v>
-      </c>
-      <c r="F28" t="s">
-        <v>227</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="B28" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H28" t="s">
+      <c r="C28" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I28" t="s">
-        <v>288</v>
+      <c r="D28" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J28">
         <v>64.3</v>
@@ -18279,73 +18479,82 @@
       <c r="GG28">
         <v>118.9</v>
       </c>
-      <c r="GH28" s="1">
+      <c r="GH28">
         <v>119.7</v>
       </c>
       <c r="GI28">
         <v>120.5</v>
       </c>
       <c r="GJ28">
-        <v>121.2</v>
+        <v>120.8</v>
       </c>
       <c r="GK28">
-        <v>121.7</v>
+        <v>120.9</v>
       </c>
       <c r="GL28">
-        <v>121.9</v>
+        <v>120.9</v>
       </c>
       <c r="GM28">
-        <v>122</v>
+        <v>121.1</v>
       </c>
       <c r="GN28">
-        <v>122.1</v>
+        <v>121.6</v>
       </c>
       <c r="GO28">
-        <v>122.2</v>
+        <v>122.3</v>
       </c>
       <c r="GP28">
-        <v>122.7</v>
+        <v>123.2</v>
       </c>
       <c r="GQ28">
-        <v>123.3</v>
+        <v>124.1</v>
       </c>
       <c r="GR28">
-        <v>123.8</v>
+        <v>124.8</v>
       </c>
       <c r="GS28">
-        <v>124.1</v>
+        <v>125.4</v>
       </c>
       <c r="GT28">
-        <v>124</v>
+        <v>125.9</v>
+      </c>
+      <c r="GU28">
+        <v>126.5</v>
+      </c>
+      <c r="GV28">
+        <v>127.1</v>
+      </c>
+      <c r="GW28">
+        <v>127.7</v>
       </c>
     </row>
-    <row r="29" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="29" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>280</v>
-      </c>
-      <c r="C29" t="s">
-        <v>281</v>
-      </c>
-      <c r="D29" t="s">
-        <v>240</v>
-      </c>
-      <c r="E29" t="s">
-        <v>231</v>
-      </c>
-      <c r="F29" t="s">
-        <v>229</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="B29" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H29" t="s">
+      <c r="C29" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I29" t="s">
-        <v>288</v>
+      <c r="D29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="J29">
         <v>60.8</v>
@@ -18887,73 +19096,82 @@
       <c r="GG29">
         <v>127.2</v>
       </c>
-      <c r="GH29" s="1">
+      <c r="GH29">
         <v>126.7</v>
       </c>
       <c r="GI29">
-        <v>126.3</v>
+        <v>126.5</v>
       </c>
       <c r="GJ29">
-        <v>126.2</v>
+        <v>126.6</v>
       </c>
       <c r="GK29">
-        <v>126.3</v>
+        <v>126.5</v>
       </c>
       <c r="GL29">
+        <v>126.4</v>
+      </c>
+      <c r="GM29">
         <v>126.5</v>
       </c>
-      <c r="GM29">
-        <v>126.6</v>
-      </c>
       <c r="GN29">
-        <v>126.6</v>
+        <v>126.9</v>
       </c>
       <c r="GO29">
-        <v>126.8</v>
+        <v>127.7</v>
       </c>
       <c r="GP29">
-        <v>127.1</v>
+        <v>128.5</v>
       </c>
       <c r="GQ29">
-        <v>127.5</v>
+        <v>129</v>
       </c>
       <c r="GR29">
-        <v>127.8</v>
+        <v>129.30000000000001</v>
       </c>
       <c r="GS29">
-        <v>128.1</v>
+        <v>129.30000000000001</v>
       </c>
       <c r="GT29">
-        <v>128.19999999999999</v>
+        <v>129.30000000000001</v>
+      </c>
+      <c r="GU29">
+        <v>129.6</v>
+      </c>
+      <c r="GV29">
+        <v>130.30000000000001</v>
+      </c>
+      <c r="GW29">
+        <v>131.19999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="30" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>280</v>
-      </c>
-      <c r="C30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D30" t="s">
-        <v>242</v>
-      </c>
-      <c r="E30" t="s">
-        <v>241</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="B30" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G30" t="s">
-        <v>283</v>
-      </c>
-      <c r="H30" t="s">
-        <v>284</v>
-      </c>
-      <c r="I30" t="s">
-        <v>289</v>
+      <c r="H30" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J30">
         <v>58.2</v>
@@ -19495,73 +19713,82 @@
       <c r="GG30">
         <v>112.5</v>
       </c>
-      <c r="GH30" s="1">
+      <c r="GH30">
         <v>112.7</v>
       </c>
       <c r="GI30">
-        <v>113.1</v>
+        <v>112.8</v>
       </c>
       <c r="GJ30">
-        <v>113.5</v>
+        <v>113.3</v>
       </c>
       <c r="GK30">
-        <v>114.1</v>
+        <v>113.9</v>
       </c>
       <c r="GL30">
-        <v>114.8</v>
+        <v>114.6</v>
       </c>
       <c r="GM30">
-        <v>115.6</v>
+        <v>115.4</v>
       </c>
       <c r="GN30">
-        <v>116.3</v>
+        <v>116.1</v>
       </c>
       <c r="GO30">
-        <v>117.1</v>
+        <v>116.9</v>
       </c>
       <c r="GP30">
-        <v>117.9</v>
+        <v>117.8</v>
       </c>
       <c r="GQ30">
-        <v>118.7</v>
+        <v>118.6</v>
       </c>
       <c r="GR30">
-        <v>119.6</v>
+        <v>119.5</v>
       </c>
       <c r="GS30">
-        <v>120.5</v>
+        <v>120.3</v>
       </c>
       <c r="GT30">
-        <v>121.3</v>
+        <v>121.1</v>
+      </c>
+      <c r="GU30">
+        <v>121.9</v>
+      </c>
+      <c r="GV30">
+        <v>122.7</v>
+      </c>
+      <c r="GW30">
+        <v>123.6</v>
       </c>
     </row>
-    <row r="31" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="31" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>280</v>
-      </c>
-      <c r="C31" t="s">
-        <v>281</v>
-      </c>
-      <c r="D31" t="s">
-        <v>243</v>
-      </c>
-      <c r="E31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F31" t="s">
-        <v>215</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="B31" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H31" t="s">
+      <c r="C31" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I31" t="s">
-        <v>289</v>
+      <c r="D31" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J31">
         <v>47.5</v>
@@ -20103,73 +20330,82 @@
       <c r="GG31">
         <v>121.3</v>
       </c>
-      <c r="GH31" s="1">
+      <c r="GH31">
         <v>121.5</v>
       </c>
       <c r="GI31">
-        <v>121.9</v>
+        <v>121.4</v>
       </c>
       <c r="GJ31">
-        <v>122.5</v>
+        <v>122.1</v>
       </c>
       <c r="GK31">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="GL31">
-        <v>124.6</v>
+        <v>124.1</v>
       </c>
       <c r="GM31">
-        <v>125.8</v>
+        <v>125.1</v>
       </c>
       <c r="GN31">
-        <v>126.9</v>
+        <v>126.3</v>
       </c>
       <c r="GO31">
-        <v>128</v>
+        <v>127.5</v>
       </c>
       <c r="GP31">
-        <v>129.19999999999999</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="GQ31">
-        <v>130.6</v>
+        <v>130</v>
       </c>
       <c r="GR31">
-        <v>132.1</v>
+        <v>131.4</v>
       </c>
       <c r="GS31">
-        <v>133.6</v>
+        <v>132.80000000000001</v>
       </c>
       <c r="GT31">
-        <v>135.1</v>
+        <v>134.19999999999999</v>
+      </c>
+      <c r="GU31">
+        <v>135.69999999999999</v>
+      </c>
+      <c r="GV31">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="GW31">
+        <v>138.69999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="32" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>280</v>
-      </c>
-      <c r="C32" t="s">
-        <v>281</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="B32" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E32" t="s">
-        <v>241</v>
-      </c>
-      <c r="F32" t="s">
-        <v>217</v>
-      </c>
-      <c r="G32" t="s">
-        <v>283</v>
-      </c>
-      <c r="H32" t="s">
-        <v>284</v>
-      </c>
-      <c r="I32" t="s">
-        <v>289</v>
+      <c r="F32" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J32">
         <v>64.3</v>
@@ -20711,73 +20947,82 @@
       <c r="GG32">
         <v>106.3</v>
       </c>
-      <c r="GH32" s="1">
+      <c r="GH32">
         <v>106.1</v>
       </c>
       <c r="GI32">
-        <v>105.7</v>
+        <v>106.2</v>
       </c>
       <c r="GJ32">
-        <v>105.1</v>
+        <v>106.5</v>
       </c>
       <c r="GK32">
-        <v>104.1</v>
+        <v>106.2</v>
       </c>
       <c r="GL32">
-        <v>103.4</v>
+        <v>105.9</v>
       </c>
       <c r="GM32">
-        <v>102.9</v>
+        <v>105.9</v>
       </c>
       <c r="GN32">
-        <v>102.9</v>
+        <v>106.5</v>
       </c>
       <c r="GO32">
-        <v>103.5</v>
+        <v>107.4</v>
       </c>
       <c r="GP32">
-        <v>104.5</v>
+        <v>108.6</v>
       </c>
       <c r="GQ32">
-        <v>105.5</v>
+        <v>109</v>
       </c>
       <c r="GR32">
-        <v>106.3</v>
+        <v>108.9</v>
       </c>
       <c r="GS32">
-        <v>106.7</v>
+        <v>108.5</v>
       </c>
       <c r="GT32">
-        <v>106.9</v>
+        <v>107.8</v>
+      </c>
+      <c r="GU32">
+        <v>107.3</v>
+      </c>
+      <c r="GV32">
+        <v>107.3</v>
+      </c>
+      <c r="GW32">
+        <v>107.8</v>
       </c>
     </row>
-    <row r="33" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="33" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>280</v>
-      </c>
-      <c r="C33" t="s">
-        <v>281</v>
-      </c>
-      <c r="D33" t="s">
-        <v>245</v>
-      </c>
-      <c r="E33" t="s">
-        <v>241</v>
-      </c>
-      <c r="F33" t="s">
-        <v>219</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="B33" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H33" t="s">
+      <c r="C33" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I33" t="s">
-        <v>289</v>
+      <c r="D33" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J33">
         <v>62.4</v>
@@ -21319,73 +21564,82 @@
       <c r="GG33">
         <v>113.9</v>
       </c>
-      <c r="GH33" s="1">
+      <c r="GH33">
         <v>114.8</v>
       </c>
       <c r="GI33">
-        <v>115.4</v>
+        <v>114.5</v>
       </c>
       <c r="GJ33">
-        <v>115.7</v>
+        <v>114.5</v>
       </c>
       <c r="GK33">
-        <v>115.8</v>
+        <v>114.6</v>
       </c>
       <c r="GL33">
-        <v>115.9</v>
+        <v>114.8</v>
       </c>
       <c r="GM33">
-        <v>115.8</v>
+        <v>114.9</v>
       </c>
       <c r="GN33">
-        <v>115.8</v>
+        <v>114.9</v>
       </c>
       <c r="GO33">
-        <v>115.7</v>
+        <v>114.9</v>
       </c>
       <c r="GP33">
-        <v>115.6</v>
+        <v>115</v>
       </c>
       <c r="GQ33">
         <v>115.6</v>
       </c>
       <c r="GR33">
-        <v>115.7</v>
+        <v>116.7</v>
       </c>
       <c r="GS33">
-        <v>116.1</v>
+        <v>118.3</v>
       </c>
       <c r="GT33">
-        <v>116.6</v>
+        <v>120</v>
+      </c>
+      <c r="GU33">
+        <v>121.3</v>
+      </c>
+      <c r="GV33">
+        <v>122.3</v>
+      </c>
+      <c r="GW33">
+        <v>122.9</v>
       </c>
     </row>
-    <row r="34" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="34" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>280</v>
-      </c>
-      <c r="C34" t="s">
-        <v>281</v>
-      </c>
-      <c r="D34" t="s">
-        <v>246</v>
-      </c>
-      <c r="E34" t="s">
-        <v>241</v>
-      </c>
-      <c r="F34" t="s">
-        <v>221</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="B34" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H34" t="s">
+      <c r="C34" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I34" t="s">
-        <v>289</v>
+      <c r="D34" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J34">
         <v>61.8</v>
@@ -21927,73 +22181,82 @@
       <c r="GG34">
         <v>116.6</v>
       </c>
-      <c r="GH34" s="1">
+      <c r="GH34">
         <v>117.8</v>
       </c>
       <c r="GI34">
-        <v>118.4</v>
+        <v>119</v>
       </c>
       <c r="GJ34">
-        <v>118.9</v>
+        <v>119.1</v>
       </c>
       <c r="GK34">
-        <v>119.3</v>
+        <v>119.2</v>
       </c>
       <c r="GL34">
-        <v>119.7</v>
+        <v>119.5</v>
       </c>
       <c r="GM34">
+        <v>119.9</v>
+      </c>
+      <c r="GN34">
         <v>120.2</v>
       </c>
-      <c r="GN34">
-        <v>120.8</v>
-      </c>
       <c r="GO34">
-        <v>121.2</v>
+        <v>120.3</v>
       </c>
       <c r="GP34">
+        <v>120.3</v>
+      </c>
+      <c r="GQ34">
+        <v>120.5</v>
+      </c>
+      <c r="GR34">
+        <v>121</v>
+      </c>
+      <c r="GS34">
         <v>121.6</v>
       </c>
-      <c r="GQ34">
-        <v>121.7</v>
-      </c>
-      <c r="GR34">
-        <v>121.8</v>
-      </c>
-      <c r="GS34">
-        <v>122.1</v>
-      </c>
       <c r="GT34">
-        <v>122.6</v>
+        <v>122.2</v>
+      </c>
+      <c r="GU34">
+        <v>122.8</v>
+      </c>
+      <c r="GV34">
+        <v>123.2</v>
+      </c>
+      <c r="GW34">
+        <v>123.6</v>
       </c>
     </row>
-    <row r="35" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="35" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>280</v>
-      </c>
-      <c r="C35" t="s">
-        <v>281</v>
-      </c>
-      <c r="D35" t="s">
-        <v>247</v>
-      </c>
-      <c r="E35" t="s">
-        <v>241</v>
-      </c>
-      <c r="F35" t="s">
-        <v>223</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="B35" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H35" t="s">
+      <c r="C35" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I35" t="s">
-        <v>289</v>
+      <c r="D35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J35">
         <v>65.099999999999994</v>
@@ -22535,73 +22798,82 @@
       <c r="GG35">
         <v>106.7</v>
       </c>
-      <c r="GH35" s="1">
+      <c r="GH35">
         <v>107.3</v>
       </c>
       <c r="GI35">
+        <v>107.3</v>
+      </c>
+      <c r="GJ35">
+        <v>107.7</v>
+      </c>
+      <c r="GK35">
         <v>107.9</v>
       </c>
-      <c r="GJ35">
-        <v>108.4</v>
-      </c>
-      <c r="GK35">
-        <v>108.8</v>
-      </c>
       <c r="GL35">
-        <v>109.1</v>
+        <v>108.1</v>
       </c>
       <c r="GM35">
-        <v>109.1</v>
+        <v>108.1</v>
       </c>
       <c r="GN35">
-        <v>109</v>
+        <v>108.3</v>
       </c>
       <c r="GO35">
-        <v>109.2</v>
+        <v>108.7</v>
       </c>
       <c r="GP35">
-        <v>109.5</v>
+        <v>109.3</v>
       </c>
       <c r="GQ35">
-        <v>110.1</v>
+        <v>110</v>
       </c>
       <c r="GR35">
-        <v>110.8</v>
+        <v>110.6</v>
       </c>
       <c r="GS35">
-        <v>111.3</v>
+        <v>111</v>
       </c>
       <c r="GT35">
-        <v>111.6</v>
+        <v>111.2</v>
+      </c>
+      <c r="GU35">
+        <v>111.2</v>
+      </c>
+      <c r="GV35">
+        <v>111.4</v>
+      </c>
+      <c r="GW35">
+        <v>111.8</v>
       </c>
     </row>
-    <row r="36" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="36" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>280</v>
-      </c>
-      <c r="C36" t="s">
-        <v>281</v>
-      </c>
-      <c r="D36" t="s">
-        <v>248</v>
-      </c>
-      <c r="E36" t="s">
-        <v>241</v>
-      </c>
-      <c r="F36" t="s">
-        <v>225</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="B36" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H36" t="s">
+      <c r="C36" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I36" t="s">
-        <v>289</v>
+      <c r="D36" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J36">
         <v>66.2</v>
@@ -23143,11 +23415,11 @@
       <c r="GG36">
         <v>106.5</v>
       </c>
-      <c r="GH36" s="1">
+      <c r="GH36">
         <v>106.9</v>
       </c>
       <c r="GI36">
-        <v>107.4</v>
+        <v>107.5</v>
       </c>
       <c r="GJ36">
         <v>107.8</v>
@@ -23162,54 +23434,63 @@
         <v>109.2</v>
       </c>
       <c r="GN36">
-        <v>109.8</v>
+        <v>109.9</v>
       </c>
       <c r="GO36">
-        <v>110.4</v>
+        <v>110.6</v>
       </c>
       <c r="GP36">
-        <v>111</v>
+        <v>111.2</v>
       </c>
       <c r="GQ36">
-        <v>111.5</v>
+        <v>111.8</v>
       </c>
       <c r="GR36">
-        <v>112</v>
+        <v>112.1</v>
       </c>
       <c r="GS36">
         <v>112.4</v>
       </c>
       <c r="GT36">
-        <v>112.8</v>
+        <v>112.5</v>
+      </c>
+      <c r="GU36">
+        <v>112.6</v>
+      </c>
+      <c r="GV36">
+        <v>112.7</v>
+      </c>
+      <c r="GW36">
+        <v>112.9</v>
       </c>
     </row>
-    <row r="37" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="37" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>280</v>
-      </c>
-      <c r="C37" t="s">
-        <v>281</v>
-      </c>
-      <c r="D37" t="s">
-        <v>249</v>
-      </c>
-      <c r="E37" t="s">
-        <v>241</v>
-      </c>
-      <c r="F37" t="s">
-        <v>227</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="B37" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H37" t="s">
+      <c r="C37" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I37" t="s">
-        <v>289</v>
+      <c r="D37" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J37">
         <v>64.400000000000006</v>
@@ -23751,73 +24032,82 @@
       <c r="GG37">
         <v>103</v>
       </c>
-      <c r="GH37" s="1">
+      <c r="GH37">
         <v>103.1</v>
       </c>
       <c r="GI37">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="GJ37">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="GK37">
-        <v>104</v>
+        <v>103.8</v>
       </c>
       <c r="GL37">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
       <c r="GM37">
-        <v>105</v>
+        <v>104.8</v>
       </c>
       <c r="GN37">
-        <v>105.7</v>
+        <v>105.4</v>
       </c>
       <c r="GO37">
-        <v>106.3</v>
+        <v>106</v>
       </c>
       <c r="GP37">
-        <v>107</v>
+        <v>106.5</v>
       </c>
       <c r="GQ37">
+        <v>106.9</v>
+      </c>
+      <c r="GR37">
+        <v>107.3</v>
+      </c>
+      <c r="GS37">
         <v>107.6</v>
       </c>
-      <c r="GR37">
-        <v>108</v>
-      </c>
-      <c r="GS37">
-        <v>108.4</v>
-      </c>
       <c r="GT37">
-        <v>108.6</v>
+        <v>107.9</v>
+      </c>
+      <c r="GU37">
+        <v>108.3</v>
+      </c>
+      <c r="GV37">
+        <v>108.7</v>
+      </c>
+      <c r="GW37">
+        <v>109.2</v>
       </c>
     </row>
-    <row r="38" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="38" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>280</v>
-      </c>
-      <c r="C38" t="s">
-        <v>281</v>
-      </c>
-      <c r="D38" t="s">
-        <v>250</v>
-      </c>
-      <c r="E38" t="s">
-        <v>241</v>
-      </c>
-      <c r="F38" t="s">
-        <v>229</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="B38" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H38" t="s">
+      <c r="C38" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I38" t="s">
-        <v>289</v>
+      <c r="D38" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="J38">
         <v>61.7</v>
@@ -24359,73 +24649,82 @@
       <c r="GG38">
         <v>110</v>
       </c>
-      <c r="GH38" s="1">
+      <c r="GH38">
         <v>109.8</v>
       </c>
       <c r="GI38">
-        <v>109.8</v>
+        <v>109.5</v>
       </c>
       <c r="GJ38">
         <v>110.1</v>
       </c>
       <c r="GK38">
-        <v>110.7</v>
+        <v>110.8</v>
       </c>
       <c r="GL38">
-        <v>111.4</v>
+        <v>111.5</v>
       </c>
       <c r="GM38">
-        <v>112.3</v>
+        <v>112.2</v>
       </c>
       <c r="GN38">
-        <v>113.1</v>
+        <v>112.8</v>
       </c>
       <c r="GO38">
-        <v>113.6</v>
+        <v>113.4</v>
       </c>
       <c r="GP38">
-        <v>114</v>
+        <v>114.1</v>
       </c>
       <c r="GQ38">
-        <v>114.5</v>
+        <v>114.8</v>
       </c>
       <c r="GR38">
-        <v>114.9</v>
+        <v>115.4</v>
       </c>
       <c r="GS38">
-        <v>115.5</v>
+        <v>116</v>
       </c>
       <c r="GT38">
-        <v>116</v>
+        <v>116.2</v>
+      </c>
+      <c r="GU38">
+        <v>116.3</v>
+      </c>
+      <c r="GV38">
+        <v>116.4</v>
+      </c>
+      <c r="GW38">
+        <v>116.5</v>
       </c>
     </row>
-    <row r="39" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A39">
+    <row r="39" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>280</v>
-      </c>
-      <c r="C39" t="s">
-        <v>281</v>
-      </c>
-      <c r="D39" t="s">
-        <v>252</v>
-      </c>
-      <c r="E39" t="s">
-        <v>251</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="B39" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G39" t="s">
-        <v>283</v>
-      </c>
-      <c r="H39" t="s">
-        <v>284</v>
-      </c>
-      <c r="I39" t="s">
-        <v>290</v>
+      <c r="H39" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J39">
         <v>61.2</v>
@@ -24967,32 +25266,32 @@
       <c r="GG39">
         <v>109.6</v>
       </c>
-      <c r="GH39" s="1">
+      <c r="GH39">
         <v>109.9</v>
       </c>
       <c r="GI39">
-        <v>110.3</v>
+        <v>110.2</v>
       </c>
       <c r="GJ39">
-        <v>110.8</v>
+        <v>110.9</v>
       </c>
       <c r="GK39">
-        <v>111.4</v>
+        <v>111.6</v>
       </c>
       <c r="GL39">
-        <v>112</v>
+        <v>112.3</v>
       </c>
       <c r="GM39">
-        <v>112.7</v>
+        <v>112.9</v>
       </c>
       <c r="GN39">
-        <v>113.3</v>
+        <v>113.4</v>
       </c>
       <c r="GO39">
-        <v>113.7</v>
+        <v>113.8</v>
       </c>
       <c r="GP39">
-        <v>114.1</v>
+        <v>114.2</v>
       </c>
       <c r="GQ39">
         <v>114.5</v>
@@ -25001,39 +25300,48 @@
         <v>114.9</v>
       </c>
       <c r="GS39">
-        <v>115.4</v>
+        <v>115.5</v>
       </c>
       <c r="GT39">
-        <v>115.9</v>
+        <v>116.1</v>
+      </c>
+      <c r="GU39">
+        <v>116.9</v>
+      </c>
+      <c r="GV39">
+        <v>117.6</v>
+      </c>
+      <c r="GW39">
+        <v>118.3</v>
       </c>
     </row>
-    <row r="40" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="40" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>280</v>
-      </c>
-      <c r="C40" t="s">
-        <v>281</v>
-      </c>
-      <c r="D40" t="s">
-        <v>253</v>
-      </c>
-      <c r="E40" t="s">
-        <v>251</v>
-      </c>
-      <c r="F40" t="s">
-        <v>215</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="B40" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H40" t="s">
+      <c r="C40" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I40" t="s">
-        <v>290</v>
+      <c r="D40" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J40">
         <v>46.7</v>
@@ -25575,23 +25883,23 @@
       <c r="GG40">
         <v>121.9</v>
       </c>
-      <c r="GH40" s="1">
+      <c r="GH40">
         <v>122.4</v>
       </c>
       <c r="GI40">
         <v>123</v>
       </c>
       <c r="GJ40">
-        <v>123.9</v>
+        <v>124.3</v>
       </c>
       <c r="GK40">
-        <v>125.2</v>
+        <v>125.7</v>
       </c>
       <c r="GL40">
-        <v>126.7</v>
+        <v>127</v>
       </c>
       <c r="GM40">
-        <v>128.1</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="GN40">
         <v>129.30000000000001</v>
@@ -25603,45 +25911,54 @@
         <v>130.80000000000001</v>
       </c>
       <c r="GQ40">
-        <v>131.6</v>
+        <v>131.5</v>
       </c>
       <c r="GR40">
-        <v>132.5</v>
+        <v>132.30000000000001</v>
       </c>
       <c r="GS40">
-        <v>133.6</v>
+        <v>133.4</v>
       </c>
       <c r="GT40">
-        <v>134.9</v>
+        <v>134.6</v>
+      </c>
+      <c r="GU40">
+        <v>135.9</v>
+      </c>
+      <c r="GV40">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="GW40">
+        <v>138.69999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A41">
+    <row r="41" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>280</v>
-      </c>
-      <c r="C41" t="s">
-        <v>281</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="B41" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E41" t="s">
-        <v>251</v>
-      </c>
-      <c r="F41" t="s">
-        <v>217</v>
-      </c>
-      <c r="G41" t="s">
-        <v>283</v>
-      </c>
-      <c r="H41" t="s">
-        <v>284</v>
-      </c>
-      <c r="I41" t="s">
-        <v>290</v>
+      <c r="F41" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J41">
         <v>76.2</v>
@@ -26183,73 +26500,82 @@
       <c r="GG41">
         <v>101.5</v>
       </c>
-      <c r="GH41" s="1">
+      <c r="GH41">
         <v>100.6</v>
       </c>
       <c r="GI41">
-        <v>100.5</v>
+        <v>100.8</v>
       </c>
       <c r="GJ41">
-        <v>101.2</v>
+        <v>103.7</v>
       </c>
       <c r="GK41">
-        <v>102.7</v>
+        <v>106.2</v>
       </c>
       <c r="GL41">
-        <v>104.5</v>
+        <v>108.4</v>
       </c>
       <c r="GM41">
-        <v>106.2</v>
+        <v>110.3</v>
       </c>
       <c r="GN41">
-        <v>108.2</v>
+        <v>112.1</v>
       </c>
       <c r="GO41">
-        <v>110.3</v>
+        <v>113.7</v>
       </c>
       <c r="GP41">
-        <v>112</v>
+        <v>114.3</v>
       </c>
       <c r="GQ41">
-        <v>112.9</v>
+        <v>113.7</v>
       </c>
       <c r="GR41">
-        <v>113</v>
+        <v>112.1</v>
       </c>
       <c r="GS41">
-        <v>112.3</v>
+        <v>110.1</v>
       </c>
       <c r="GT41">
-        <v>111.2</v>
+        <v>108.1</v>
+      </c>
+      <c r="GU41">
+        <v>106.7</v>
+      </c>
+      <c r="GV41">
+        <v>106.3</v>
+      </c>
+      <c r="GW41">
+        <v>106.7</v>
       </c>
     </row>
-    <row r="42" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="42" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>280</v>
-      </c>
-      <c r="C42" t="s">
-        <v>281</v>
-      </c>
-      <c r="D42" t="s">
-        <v>255</v>
-      </c>
-      <c r="E42" t="s">
-        <v>251</v>
-      </c>
-      <c r="F42" t="s">
-        <v>219</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="B42" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H42" t="s">
+      <c r="C42" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I42" t="s">
-        <v>290</v>
+      <c r="D42" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J42">
         <v>67.099999999999994</v>
@@ -26791,73 +27117,82 @@
       <c r="GG42">
         <v>109.6</v>
       </c>
-      <c r="GH42" s="1">
+      <c r="GH42">
         <v>109.5</v>
       </c>
       <c r="GI42">
-        <v>109.3</v>
+        <v>110.2</v>
       </c>
       <c r="GJ42">
-        <v>109</v>
+        <v>110.4</v>
       </c>
       <c r="GK42">
-        <v>108.8</v>
+        <v>110.5</v>
       </c>
       <c r="GL42">
-        <v>108.8</v>
+        <v>110.6</v>
       </c>
       <c r="GM42">
-        <v>109.1</v>
+        <v>110.7</v>
       </c>
       <c r="GN42">
-        <v>109.4</v>
+        <v>110.7</v>
       </c>
       <c r="GO42">
-        <v>109.6</v>
+        <v>110.8</v>
       </c>
       <c r="GP42">
-        <v>109.9</v>
+        <v>111</v>
       </c>
       <c r="GQ42">
-        <v>110.2</v>
+        <v>111.6</v>
       </c>
       <c r="GR42">
-        <v>110.6</v>
+        <v>112.5</v>
       </c>
       <c r="GS42">
-        <v>111</v>
+        <v>113.7</v>
       </c>
       <c r="GT42">
-        <v>111.5</v>
+        <v>114.9</v>
+      </c>
+      <c r="GU42">
+        <v>115.8</v>
+      </c>
+      <c r="GV42">
+        <v>116.3</v>
+      </c>
+      <c r="GW42">
+        <v>116.5</v>
       </c>
     </row>
-    <row r="43" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A43">
+    <row r="43" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>280</v>
-      </c>
-      <c r="C43" t="s">
-        <v>281</v>
-      </c>
-      <c r="D43" t="s">
-        <v>256</v>
-      </c>
-      <c r="E43" t="s">
-        <v>251</v>
-      </c>
-      <c r="F43" t="s">
-        <v>221</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="B43" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H43" t="s">
+      <c r="C43" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I43" t="s">
-        <v>290</v>
+      <c r="D43" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J43">
         <v>74</v>
@@ -27399,73 +27734,82 @@
       <c r="GG43">
         <v>115.2</v>
       </c>
-      <c r="GH43" s="1">
+      <c r="GH43">
         <v>115.9</v>
       </c>
       <c r="GI43">
-        <v>116.3</v>
+        <v>116.7</v>
       </c>
       <c r="GJ43">
-        <v>116.7</v>
+        <v>117.1</v>
       </c>
       <c r="GK43">
-        <v>117.3</v>
+        <v>117.8</v>
       </c>
       <c r="GL43">
-        <v>117.9</v>
+        <v>118.8</v>
       </c>
       <c r="GM43">
-        <v>118.6</v>
+        <v>119.7</v>
       </c>
       <c r="GN43">
-        <v>119.3</v>
+        <v>120.7</v>
       </c>
       <c r="GO43">
-        <v>119.9</v>
+        <v>121.5</v>
       </c>
       <c r="GP43">
-        <v>120.2</v>
+        <v>122.2</v>
       </c>
       <c r="GQ43">
-        <v>120.1</v>
+        <v>122.7</v>
       </c>
       <c r="GR43">
-        <v>120</v>
+        <v>123.5</v>
       </c>
       <c r="GS43">
-        <v>120</v>
+        <v>124.7</v>
       </c>
       <c r="GT43">
-        <v>120.3</v>
+        <v>125.7</v>
+      </c>
+      <c r="GU43">
+        <v>126.5</v>
+      </c>
+      <c r="GV43">
+        <v>127.1</v>
+      </c>
+      <c r="GW43">
+        <v>127.5</v>
       </c>
     </row>
-    <row r="44" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="44" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>280</v>
-      </c>
-      <c r="C44" t="s">
-        <v>281</v>
-      </c>
-      <c r="D44" t="s">
-        <v>257</v>
-      </c>
-      <c r="E44" t="s">
-        <v>251</v>
-      </c>
-      <c r="F44" t="s">
-        <v>223</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="B44" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H44" t="s">
+      <c r="C44" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I44" t="s">
-        <v>290</v>
+      <c r="D44" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J44">
         <v>67.2</v>
@@ -28007,73 +28351,82 @@
       <c r="GG44">
         <v>102.8</v>
       </c>
-      <c r="GH44" s="1">
+      <c r="GH44">
         <v>102.5</v>
       </c>
       <c r="GI44">
-        <v>102.2</v>
+        <v>101.9</v>
       </c>
       <c r="GJ44">
-        <v>102</v>
+        <v>102.3</v>
       </c>
       <c r="GK44">
-        <v>102</v>
+        <v>102.9</v>
       </c>
       <c r="GL44">
-        <v>102.3</v>
+        <v>103.5</v>
       </c>
       <c r="GM44">
-        <v>102.6</v>
+        <v>104.1</v>
       </c>
       <c r="GN44">
-        <v>103</v>
+        <v>104.6</v>
       </c>
       <c r="GO44">
-        <v>103.5</v>
+        <v>104.9</v>
       </c>
       <c r="GP44">
-        <v>104</v>
+        <v>105.3</v>
       </c>
       <c r="GQ44">
-        <v>104.5</v>
+        <v>105.6</v>
       </c>
       <c r="GR44">
-        <v>104.9</v>
+        <v>106</v>
       </c>
       <c r="GS44">
-        <v>105.4</v>
+        <v>106.4</v>
       </c>
       <c r="GT44">
-        <v>105.7</v>
+        <v>107</v>
+      </c>
+      <c r="GU44">
+        <v>107.5</v>
+      </c>
+      <c r="GV44">
+        <v>108</v>
+      </c>
+      <c r="GW44">
+        <v>108.4</v>
       </c>
     </row>
-    <row r="45" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A45">
+    <row r="45" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>280</v>
-      </c>
-      <c r="C45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D45" t="s">
-        <v>258</v>
-      </c>
-      <c r="E45" t="s">
-        <v>251</v>
-      </c>
-      <c r="F45" t="s">
-        <v>225</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="B45" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H45" t="s">
+      <c r="C45" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I45" t="s">
-        <v>290</v>
+      <c r="D45" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J45">
         <v>68.8</v>
@@ -28615,73 +28968,82 @@
       <c r="GG45">
         <v>99.3</v>
       </c>
-      <c r="GH45" s="1">
+      <c r="GH45">
         <v>99.1</v>
       </c>
       <c r="GI45">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="GJ45">
-        <v>99</v>
+        <v>99.7</v>
       </c>
       <c r="GK45">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="GL45">
-        <v>98.9</v>
+        <v>99.3</v>
       </c>
       <c r="GM45">
-        <v>98.7</v>
+        <v>99.1</v>
       </c>
       <c r="GN45">
-        <v>98.5</v>
+        <v>99.2</v>
       </c>
       <c r="GO45">
-        <v>98.6</v>
+        <v>99.4</v>
       </c>
       <c r="GP45">
-        <v>98.9</v>
+        <v>99.9</v>
       </c>
       <c r="GQ45">
-        <v>99.4</v>
+        <v>100.6</v>
       </c>
       <c r="GR45">
-        <v>100</v>
+        <v>101.1</v>
       </c>
       <c r="GS45">
-        <v>100.5</v>
+        <v>101.5</v>
       </c>
       <c r="GT45">
-        <v>100.8</v>
+        <v>101.6</v>
+      </c>
+      <c r="GU45">
+        <v>101.5</v>
+      </c>
+      <c r="GV45">
+        <v>101.2</v>
+      </c>
+      <c r="GW45">
+        <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A46">
+    <row r="46" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>280</v>
-      </c>
-      <c r="C46" t="s">
-        <v>281</v>
-      </c>
-      <c r="D46" t="s">
-        <v>259</v>
-      </c>
-      <c r="E46" t="s">
-        <v>251</v>
-      </c>
-      <c r="F46" t="s">
-        <v>227</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="B46" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H46" t="s">
+      <c r="C46" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I46" t="s">
-        <v>290</v>
+      <c r="D46" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J46">
         <v>65.2</v>
@@ -29223,73 +29585,82 @@
       <c r="GG46">
         <v>98.3</v>
       </c>
-      <c r="GH46" s="1">
+      <c r="GH46">
         <v>98.9</v>
       </c>
       <c r="GI46">
+        <v>99</v>
+      </c>
+      <c r="GJ46">
         <v>99.4</v>
       </c>
-      <c r="GJ46">
+      <c r="GK46">
+        <v>99.5</v>
+      </c>
+      <c r="GL46">
+        <v>99.6</v>
+      </c>
+      <c r="GM46">
         <v>99.7</v>
       </c>
-      <c r="GK46">
+      <c r="GN46">
+        <v>99.8</v>
+      </c>
+      <c r="GO46">
+        <v>99.8</v>
+      </c>
+      <c r="GP46">
         <v>99.7</v>
       </c>
-      <c r="GL46">
-        <v>99.8</v>
-      </c>
-      <c r="GM46">
-        <v>99.8</v>
-      </c>
-      <c r="GN46">
+      <c r="GQ46">
+        <v>99.6</v>
+      </c>
+      <c r="GR46">
+        <v>99.3</v>
+      </c>
+      <c r="GS46">
+        <v>99.2</v>
+      </c>
+      <c r="GT46">
+        <v>99.2</v>
+      </c>
+      <c r="GU46">
+        <v>99.4</v>
+      </c>
+      <c r="GV46">
+        <v>99.7</v>
+      </c>
+      <c r="GW46">
         <v>100</v>
       </c>
-      <c r="GO46">
-        <v>100.1</v>
-      </c>
-      <c r="GP46">
-        <v>100.3</v>
-      </c>
-      <c r="GQ46">
-        <v>100.2</v>
-      </c>
-      <c r="GR46">
-        <v>99.9</v>
-      </c>
-      <c r="GS46">
-        <v>99.5</v>
-      </c>
-      <c r="GT46">
-        <v>99.1</v>
-      </c>
     </row>
-    <row r="47" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="47" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>280</v>
-      </c>
-      <c r="C47" t="s">
-        <v>281</v>
-      </c>
-      <c r="D47" t="s">
-        <v>260</v>
-      </c>
-      <c r="E47" t="s">
-        <v>251</v>
-      </c>
-      <c r="F47" t="s">
-        <v>229</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="B47" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H47" t="s">
+      <c r="C47" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I47" t="s">
-        <v>290</v>
+      <c r="D47" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="J47">
         <v>65.2</v>
@@ -29831,73 +30202,82 @@
       <c r="GG47">
         <v>112.9</v>
       </c>
-      <c r="GH47" s="1">
+      <c r="GH47">
         <v>113.3</v>
       </c>
       <c r="GI47">
+        <v>113.6</v>
+      </c>
+      <c r="GJ47">
+        <v>113.7</v>
+      </c>
+      <c r="GK47">
         <v>113.8</v>
       </c>
-      <c r="GJ47">
+      <c r="GL47">
+        <v>114</v>
+      </c>
+      <c r="GM47">
+        <v>114.1</v>
+      </c>
+      <c r="GN47">
+        <v>114.2</v>
+      </c>
+      <c r="GO47">
         <v>114.3</v>
       </c>
-      <c r="GK47">
+      <c r="GP47">
+        <v>114.3</v>
+      </c>
+      <c r="GQ47">
+        <v>114.3</v>
+      </c>
+      <c r="GR47">
+        <v>114.4</v>
+      </c>
+      <c r="GS47">
+        <v>114.5</v>
+      </c>
+      <c r="GT47">
         <v>114.8</v>
       </c>
-      <c r="GL47">
+      <c r="GU47">
         <v>115.1</v>
       </c>
-      <c r="GM47">
-        <v>115.3</v>
-      </c>
-      <c r="GN47">
+      <c r="GV47">
         <v>115.5</v>
       </c>
-      <c r="GO47">
-        <v>115.6</v>
-      </c>
-      <c r="GP47">
-        <v>115.6</v>
-      </c>
-      <c r="GQ47">
-        <v>115.7</v>
-      </c>
-      <c r="GR47">
+      <c r="GW47">
         <v>115.8</v>
       </c>
-      <c r="GS47">
-        <v>116</v>
-      </c>
-      <c r="GT47">
-        <v>116.2</v>
-      </c>
     </row>
-    <row r="48" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A48">
+    <row r="48" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>280</v>
-      </c>
-      <c r="C48" t="s">
-        <v>281</v>
-      </c>
-      <c r="D48" t="s">
-        <v>262</v>
-      </c>
-      <c r="E48" t="s">
-        <v>261</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="B48" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G48" t="s">
-        <v>283</v>
-      </c>
-      <c r="H48" t="s">
-        <v>284</v>
-      </c>
-      <c r="I48" t="s">
-        <v>291</v>
+      <c r="H48" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J48">
         <v>55.6</v>
@@ -30439,73 +30819,82 @@
       <c r="GG48">
         <v>114.1</v>
       </c>
-      <c r="GH48" s="1">
+      <c r="GH48">
         <v>114.2</v>
       </c>
       <c r="GI48">
-        <v>114.6</v>
+        <v>114.4</v>
       </c>
       <c r="GJ48">
-        <v>115.2</v>
+        <v>115</v>
       </c>
       <c r="GK48">
-        <v>116.1</v>
+        <v>115.7</v>
       </c>
       <c r="GL48">
-        <v>117</v>
+        <v>116.4</v>
       </c>
       <c r="GM48">
+        <v>117.2</v>
+      </c>
+      <c r="GN48">
         <v>118.1</v>
       </c>
-      <c r="GN48">
+      <c r="GO48">
         <v>119</v>
       </c>
-      <c r="GO48">
-        <v>119.9</v>
-      </c>
       <c r="GP48">
-        <v>120.9</v>
+        <v>120</v>
       </c>
       <c r="GQ48">
+        <v>121.1</v>
+      </c>
+      <c r="GR48">
         <v>122.1</v>
       </c>
-      <c r="GR48">
-        <v>123.4</v>
-      </c>
       <c r="GS48">
-        <v>124.5</v>
+        <v>123</v>
       </c>
       <c r="GT48">
-        <v>125.5</v>
+        <v>123.9</v>
+      </c>
+      <c r="GU48">
+        <v>124.6</v>
+      </c>
+      <c r="GV48">
+        <v>125.2</v>
+      </c>
+      <c r="GW48">
+        <v>125.9</v>
       </c>
     </row>
-    <row r="49" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A49">
+    <row r="49" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>280</v>
-      </c>
-      <c r="C49" t="s">
-        <v>281</v>
-      </c>
-      <c r="D49" t="s">
-        <v>263</v>
-      </c>
-      <c r="E49" t="s">
-        <v>261</v>
-      </c>
-      <c r="F49" t="s">
-        <v>215</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="B49" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H49" t="s">
+      <c r="C49" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I49" t="s">
-        <v>291</v>
+      <c r="D49" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J49">
         <v>50.6</v>
@@ -31047,73 +31436,82 @@
       <c r="GG49">
         <v>118.5</v>
       </c>
-      <c r="GH49" s="1">
+      <c r="GH49">
         <v>118.8</v>
       </c>
       <c r="GI49">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="GJ49">
-        <v>120.6</v>
+        <v>120.2</v>
       </c>
       <c r="GK49">
-        <v>122.1</v>
+        <v>121.4</v>
       </c>
       <c r="GL49">
-        <v>123.6</v>
+        <v>122.5</v>
       </c>
       <c r="GM49">
-        <v>125</v>
+        <v>123.5</v>
       </c>
       <c r="GN49">
-        <v>126.1</v>
+        <v>124.5</v>
       </c>
       <c r="GO49">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="GP49">
+        <v>126.7</v>
+      </c>
+      <c r="GQ49">
         <v>128.1</v>
       </c>
-      <c r="GQ49">
+      <c r="GR49">
         <v>129.5</v>
       </c>
-      <c r="GR49">
-        <v>131.19999999999999</v>
-      </c>
       <c r="GS49">
-        <v>132.9</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="GT49">
-        <v>134.5</v>
+        <v>131.9</v>
+      </c>
+      <c r="GU49">
+        <v>132.69999999999999</v>
+      </c>
+      <c r="GV49">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="GW49">
+        <v>133.80000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A50">
+    <row r="50" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>280</v>
-      </c>
-      <c r="C50" t="s">
-        <v>281</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="B50" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E50" t="s">
-        <v>261</v>
-      </c>
-      <c r="F50" t="s">
-        <v>217</v>
-      </c>
-      <c r="G50" t="s">
-        <v>283</v>
-      </c>
-      <c r="H50" t="s">
-        <v>284</v>
-      </c>
-      <c r="I50" t="s">
-        <v>291</v>
+      <c r="F50" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J50">
         <v>62.2</v>
@@ -31655,73 +32053,82 @@
       <c r="GG50">
         <v>103.4</v>
       </c>
-      <c r="GH50" s="1">
+      <c r="GH50">
         <v>102.6</v>
       </c>
       <c r="GI50">
-        <v>102.1</v>
+        <v>103.5</v>
       </c>
       <c r="GJ50">
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="GK50">
-        <v>102.2</v>
+        <v>103.9</v>
       </c>
       <c r="GL50">
-        <v>102.6</v>
+        <v>104.7</v>
       </c>
       <c r="GM50">
-        <v>103</v>
+        <v>105.8</v>
       </c>
       <c r="GN50">
-        <v>103.6</v>
+        <v>106.8</v>
       </c>
       <c r="GO50">
-        <v>104.7</v>
+        <v>107.7</v>
       </c>
       <c r="GP50">
-        <v>105.9</v>
+        <v>108.3</v>
       </c>
       <c r="GQ50">
-        <v>107.3</v>
+        <v>108.6</v>
       </c>
       <c r="GR50">
-        <v>108.5</v>
+        <v>108.7</v>
       </c>
       <c r="GS50">
-        <v>109.2</v>
+        <v>109.3</v>
       </c>
       <c r="GT50">
-        <v>109.5</v>
+        <v>110</v>
+      </c>
+      <c r="GU50">
+        <v>110.7</v>
+      </c>
+      <c r="GV50">
+        <v>111.5</v>
+      </c>
+      <c r="GW50">
+        <v>112.2</v>
       </c>
     </row>
-    <row r="51" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A51">
+    <row r="51" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
-        <v>280</v>
-      </c>
-      <c r="C51" t="s">
-        <v>281</v>
-      </c>
-      <c r="D51" t="s">
-        <v>265</v>
-      </c>
-      <c r="E51" t="s">
-        <v>261</v>
-      </c>
-      <c r="F51" t="s">
-        <v>219</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="B51" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H51" t="s">
+      <c r="C51" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I51" t="s">
-        <v>291</v>
+      <c r="D51" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J51">
         <v>63.6</v>
@@ -32263,73 +32670,82 @@
       <c r="GG51">
         <v>116.4</v>
       </c>
-      <c r="GH51" s="1">
+      <c r="GH51">
         <v>115.3</v>
       </c>
       <c r="GI51">
-        <v>114.7</v>
+        <v>114.6</v>
       </c>
       <c r="GJ51">
-        <v>114.5</v>
+        <v>115.4</v>
       </c>
       <c r="GK51">
-        <v>114.8</v>
+        <v>116.4</v>
       </c>
       <c r="GL51">
-        <v>115.3</v>
+        <v>117.3</v>
       </c>
       <c r="GM51">
-        <v>115.8</v>
+        <v>118.2</v>
       </c>
       <c r="GN51">
-        <v>116.3</v>
+        <v>118.8</v>
       </c>
       <c r="GO51">
-        <v>117</v>
+        <v>119.4</v>
       </c>
       <c r="GP51">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="GQ51">
-        <v>119</v>
+        <v>120.7</v>
       </c>
       <c r="GR51">
-        <v>119.9</v>
+        <v>121.6</v>
       </c>
       <c r="GS51">
-        <v>120.8</v>
+        <v>122.6</v>
       </c>
       <c r="GT51">
-        <v>121.5</v>
+        <v>123.2</v>
+      </c>
+      <c r="GU51">
+        <v>123.5</v>
+      </c>
+      <c r="GV51">
+        <v>123.6</v>
+      </c>
+      <c r="GW51">
+        <v>123.6</v>
       </c>
     </row>
-    <row r="52" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A52">
+    <row r="52" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>280</v>
-      </c>
-      <c r="C52" t="s">
-        <v>281</v>
-      </c>
-      <c r="D52" t="s">
-        <v>266</v>
-      </c>
-      <c r="E52" t="s">
-        <v>261</v>
-      </c>
-      <c r="F52" t="s">
-        <v>221</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="B52" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H52" t="s">
+      <c r="C52" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I52" t="s">
-        <v>291</v>
+      <c r="D52" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J52">
         <v>53</v>
@@ -32871,73 +33287,82 @@
       <c r="GG52">
         <v>108.1</v>
       </c>
-      <c r="GH52" s="1">
+      <c r="GH52">
         <v>108.7</v>
       </c>
       <c r="GI52">
-        <v>109.8</v>
+        <v>109.5</v>
       </c>
       <c r="GJ52">
+        <v>110.6</v>
+      </c>
+      <c r="GK52">
+        <v>111.6</v>
+      </c>
+      <c r="GL52">
+        <v>112.1</v>
+      </c>
+      <c r="GM52">
+        <v>112.1</v>
+      </c>
+      <c r="GN52">
+        <v>111.7</v>
+      </c>
+      <c r="GO52">
+        <v>110.7</v>
+      </c>
+      <c r="GP52">
+        <v>109.5</v>
+      </c>
+      <c r="GQ52">
+        <v>108.7</v>
+      </c>
+      <c r="GR52">
+        <v>108.5</v>
+      </c>
+      <c r="GS52">
+        <v>109</v>
+      </c>
+      <c r="GT52">
+        <v>110</v>
+      </c>
+      <c r="GU52">
         <v>111.1</v>
       </c>
-      <c r="GK52">
-        <v>112.8</v>
-      </c>
-      <c r="GL52">
-        <v>114.3</v>
-      </c>
-      <c r="GM52">
-        <v>115.8</v>
-      </c>
-      <c r="GN52">
-        <v>117.1</v>
-      </c>
-      <c r="GO52">
-        <v>117.9</v>
-      </c>
-      <c r="GP52">
-        <v>118.2</v>
-      </c>
-      <c r="GQ52">
-        <v>118</v>
-      </c>
-      <c r="GR52">
-        <v>118</v>
-      </c>
-      <c r="GS52">
-        <v>118.3</v>
-      </c>
-      <c r="GT52">
-        <v>119</v>
+      <c r="GV52">
+        <v>112.4</v>
+      </c>
+      <c r="GW52">
+        <v>113.4</v>
       </c>
     </row>
-    <row r="53" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A53">
+    <row r="53" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>280</v>
-      </c>
-      <c r="C53" t="s">
-        <v>281</v>
-      </c>
-      <c r="D53" t="s">
-        <v>267</v>
-      </c>
-      <c r="E53" t="s">
-        <v>261</v>
-      </c>
-      <c r="F53" t="s">
-        <v>223</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="B53" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H53" t="s">
+      <c r="C53" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I53" t="s">
-        <v>291</v>
+      <c r="D53" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J53">
         <v>61.8</v>
@@ -33479,73 +33904,82 @@
       <c r="GG53">
         <v>110.5</v>
       </c>
-      <c r="GH53" s="1">
+      <c r="GH53">
         <v>111.8</v>
       </c>
       <c r="GI53">
-        <v>112.9</v>
+        <v>112</v>
       </c>
       <c r="GJ53">
+        <v>112</v>
+      </c>
+      <c r="GK53">
+        <v>111.9</v>
+      </c>
+      <c r="GL53">
+        <v>111.7</v>
+      </c>
+      <c r="GM53">
+        <v>111.7</v>
+      </c>
+      <c r="GN53">
+        <v>111.7</v>
+      </c>
+      <c r="GO53">
+        <v>111.9</v>
+      </c>
+      <c r="GP53">
+        <v>112.2</v>
+      </c>
+      <c r="GQ53">
+        <v>112.6</v>
+      </c>
+      <c r="GR53">
+        <v>113.1</v>
+      </c>
+      <c r="GS53">
         <v>113.8</v>
       </c>
-      <c r="GK53">
-        <v>114.5</v>
-      </c>
-      <c r="GL53">
-        <v>114.9</v>
-      </c>
-      <c r="GM53">
-        <v>115.3</v>
-      </c>
-      <c r="GN53">
-        <v>115.7</v>
-      </c>
-      <c r="GO53">
-        <v>116.1</v>
-      </c>
-      <c r="GP53">
-        <v>116.6</v>
-      </c>
-      <c r="GQ53">
-        <v>117.2</v>
-      </c>
-      <c r="GR53">
-        <v>117.7</v>
-      </c>
-      <c r="GS53">
-        <v>118</v>
-      </c>
       <c r="GT53">
-        <v>118.1</v>
+        <v>114.3</v>
+      </c>
+      <c r="GU53">
+        <v>114.8</v>
+      </c>
+      <c r="GV53">
+        <v>115.2</v>
+      </c>
+      <c r="GW53">
+        <v>115.8</v>
       </c>
     </row>
-    <row r="54" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A54">
+    <row r="54" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>280</v>
-      </c>
-      <c r="C54" t="s">
-        <v>281</v>
-      </c>
-      <c r="D54" t="s">
-        <v>268</v>
-      </c>
-      <c r="E54" t="s">
-        <v>261</v>
-      </c>
-      <c r="F54" t="s">
-        <v>225</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="B54" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H54" t="s">
+      <c r="C54" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I54" t="s">
-        <v>291</v>
+      <c r="D54" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J54">
         <v>58</v>
@@ -34087,73 +34521,82 @@
       <c r="GG54">
         <v>113.1</v>
       </c>
-      <c r="GH54" s="1">
+      <c r="GH54">
         <v>113.5</v>
       </c>
       <c r="GI54">
         <v>114</v>
       </c>
       <c r="GJ54">
+        <v>114</v>
+      </c>
+      <c r="GK54">
+        <v>113.8</v>
+      </c>
+      <c r="GL54">
+        <v>113.7</v>
+      </c>
+      <c r="GM54">
+        <v>113.8</v>
+      </c>
+      <c r="GN54">
         <v>114.3</v>
       </c>
-      <c r="GK54">
-        <v>114.6</v>
-      </c>
-      <c r="GL54">
-        <v>114.8</v>
-      </c>
-      <c r="GM54">
-        <v>115.2</v>
-      </c>
-      <c r="GN54">
-        <v>115.9</v>
-      </c>
       <c r="GO54">
-        <v>116.6</v>
+        <v>115.3</v>
       </c>
       <c r="GP54">
+        <v>116.5</v>
+      </c>
+      <c r="GQ54">
         <v>117.6</v>
       </c>
-      <c r="GQ54">
-        <v>118.6</v>
-      </c>
       <c r="GR54">
+        <v>118.5</v>
+      </c>
+      <c r="GS54">
+        <v>119.1</v>
+      </c>
+      <c r="GT54">
         <v>119.5</v>
       </c>
-      <c r="GS54">
-        <v>120.3</v>
-      </c>
-      <c r="GT54">
-        <v>120.9</v>
+      <c r="GU54">
+        <v>119.9</v>
+      </c>
+      <c r="GV54">
+        <v>120.4</v>
+      </c>
+      <c r="GW54">
+        <v>121</v>
       </c>
     </row>
-    <row r="55" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A55">
+    <row r="55" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>280</v>
-      </c>
-      <c r="C55" t="s">
-        <v>281</v>
-      </c>
-      <c r="D55" t="s">
-        <v>269</v>
-      </c>
-      <c r="E55" t="s">
-        <v>261</v>
-      </c>
-      <c r="F55" t="s">
-        <v>227</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="B55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H55" t="s">
+      <c r="C55" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I55" t="s">
-        <v>291</v>
+      <c r="D55" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J55">
         <v>58.3</v>
@@ -34695,73 +35138,82 @@
       <c r="GG55">
         <v>108.3</v>
       </c>
-      <c r="GH55" s="1">
+      <c r="GH55">
         <v>108.3</v>
       </c>
       <c r="GI55">
-        <v>108.2</v>
+        <v>108.6</v>
       </c>
       <c r="GJ55">
-        <v>108.4</v>
+        <v>108.8</v>
       </c>
       <c r="GK55">
-        <v>108.8</v>
+        <v>109.3</v>
       </c>
       <c r="GL55">
-        <v>109.4</v>
+        <v>110.1</v>
       </c>
       <c r="GM55">
-        <v>110.2</v>
+        <v>111</v>
       </c>
       <c r="GN55">
-        <v>111.2</v>
+        <v>112.1</v>
       </c>
       <c r="GO55">
-        <v>112.3</v>
+        <v>113.2</v>
       </c>
       <c r="GP55">
-        <v>113.5</v>
+        <v>114.3</v>
       </c>
       <c r="GQ55">
-        <v>114.8</v>
+        <v>115.2</v>
       </c>
       <c r="GR55">
-        <v>115.7</v>
+        <v>116.1</v>
       </c>
       <c r="GS55">
-        <v>116.6</v>
+        <v>117.1</v>
       </c>
       <c r="GT55">
-        <v>117.2</v>
+        <v>118.1</v>
+      </c>
+      <c r="GU55">
+        <v>119.2</v>
+      </c>
+      <c r="GV55">
+        <v>120.2</v>
+      </c>
+      <c r="GW55">
+        <v>121.1</v>
       </c>
     </row>
-    <row r="56" spans="1:202" x14ac:dyDescent="0.3">
-      <c r="A56">
+    <row r="56" spans="1:205" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>280</v>
-      </c>
-      <c r="C56" t="s">
-        <v>281</v>
-      </c>
-      <c r="D56" t="s">
-        <v>270</v>
-      </c>
-      <c r="E56" t="s">
-        <v>261</v>
-      </c>
-      <c r="F56" t="s">
-        <v>229</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="B56" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H56" t="s">
+      <c r="C56" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I56" t="s">
-        <v>291</v>
+      <c r="D56" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="J56">
         <v>55.9</v>
@@ -35303,44 +35755,53 @@
       <c r="GG56">
         <v>115</v>
       </c>
-      <c r="GH56" s="1">
+      <c r="GH56">
         <v>114.6</v>
       </c>
       <c r="GI56">
-        <v>114.3</v>
+        <v>114.5</v>
       </c>
       <c r="GJ56">
-        <v>114.5</v>
+        <v>115</v>
       </c>
       <c r="GK56">
-        <v>115.1</v>
+        <v>116</v>
       </c>
       <c r="GL56">
-        <v>116.1</v>
+        <v>117.3</v>
       </c>
       <c r="GM56">
-        <v>117.1</v>
+        <v>118.5</v>
       </c>
       <c r="GN56">
-        <v>118.2</v>
+        <v>119.5</v>
       </c>
       <c r="GO56">
-        <v>119.3</v>
+        <v>120.5</v>
       </c>
       <c r="GP56">
-        <v>120.5</v>
+        <v>121.3</v>
       </c>
       <c r="GQ56">
-        <v>121.5</v>
+        <v>122</v>
       </c>
       <c r="GR56">
         <v>122.6</v>
       </c>
       <c r="GS56">
-        <v>123.4</v>
+        <v>123.3</v>
       </c>
       <c r="GT56">
-        <v>124.2</v>
+        <v>123.9</v>
+      </c>
+      <c r="GU56">
+        <v>124.6</v>
+      </c>
+      <c r="GV56">
+        <v>125.1</v>
+      </c>
+      <c r="GW56">
+        <v>125.6</v>
       </c>
     </row>
   </sheetData>
